--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="633">
   <si>
     <t>id</t>
   </si>
@@ -1766,6 +1766,9 @@
   </si>
   <si>
     <t>collection.star_gold_multiplier</t>
+  </si>
+  <si>
+    <t>collection.close_gold_seconds_per_star</t>
   </si>
   <si>
     <t>collection.vault_gold_stars</t>
@@ -10521,7 +10524,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -10948,7 +10951,7 @@
         <v>566</v>
       </c>
       <c r="B53">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -11020,7 +11023,7 @@
         <v>579</v>
       </c>
       <c r="B62">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -11028,23 +11031,23 @@
         <v>580</v>
       </c>
       <c r="B63">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>581</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>582</v>
+      <c r="B64">
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>582</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -11052,7 +11055,7 @@
         <v>584</v>
       </c>
       <c r="B66">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -11060,7 +11063,7 @@
         <v>585</v>
       </c>
       <c r="B67">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -11068,7 +11071,7 @@
         <v>586</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -11076,7 +11079,7 @@
         <v>587</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -11084,7 +11087,7 @@
         <v>588</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -11092,7 +11095,7 @@
         <v>589</v>
       </c>
       <c r="B71">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -11100,7 +11103,7 @@
         <v>590</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -11108,7 +11111,7 @@
         <v>591</v>
       </c>
       <c r="B73">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -11116,7 +11119,7 @@
         <v>592</v>
       </c>
       <c r="B74">
-        <v>1.09</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -11124,7 +11127,7 @@
         <v>593</v>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -11132,7 +11135,7 @@
         <v>594</v>
       </c>
       <c r="B76">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -11140,7 +11143,7 @@
         <v>595</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -11148,7 +11151,7 @@
         <v>596</v>
       </c>
       <c r="B78">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -11164,7 +11167,7 @@
         <v>598</v>
       </c>
       <c r="B80">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -11172,7 +11175,7 @@
         <v>599</v>
       </c>
       <c r="B81">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -11180,7 +11183,7 @@
         <v>600</v>
       </c>
       <c r="B82">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -11188,7 +11191,7 @@
         <v>601</v>
       </c>
       <c r="B83">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -11196,7 +11199,7 @@
         <v>602</v>
       </c>
       <c r="B84">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -11204,7 +11207,7 @@
         <v>603</v>
       </c>
       <c r="B85">
-        <v>100</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -11212,7 +11215,7 @@
         <v>604</v>
       </c>
       <c r="B86">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -11220,7 +11223,7 @@
         <v>605</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -11228,7 +11231,7 @@
         <v>606</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -11236,7 +11239,7 @@
         <v>607</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -11244,7 +11247,7 @@
         <v>608</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -11252,7 +11255,7 @@
         <v>609</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -11260,7 +11263,7 @@
         <v>610</v>
       </c>
       <c r="B92">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -11268,7 +11271,7 @@
         <v>611</v>
       </c>
       <c r="B93">
-        <v>400</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -11276,7 +11279,7 @@
         <v>612</v>
       </c>
       <c r="B94">
-        <v>0.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -11284,7 +11287,7 @@
         <v>613</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -11292,7 +11295,7 @@
         <v>614</v>
       </c>
       <c r="B96">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -11300,7 +11303,7 @@
         <v>615</v>
       </c>
       <c r="B97">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -11308,7 +11311,7 @@
         <v>616</v>
       </c>
       <c r="B98">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -11316,7 +11319,7 @@
         <v>617</v>
       </c>
       <c r="B99">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -11324,7 +11327,7 @@
         <v>618</v>
       </c>
       <c r="B100">
-        <v>500</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -11332,7 +11335,7 @@
         <v>619</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -11340,7 +11343,7 @@
         <v>620</v>
       </c>
       <c r="B102">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -11348,7 +11351,7 @@
         <v>621</v>
       </c>
       <c r="B103">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -11356,7 +11359,7 @@
         <v>622</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -11364,7 +11367,7 @@
         <v>623</v>
       </c>
       <c r="B105">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -11372,7 +11375,7 @@
         <v>624</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -11380,7 +11383,7 @@
         <v>625</v>
       </c>
       <c r="B107">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -11388,7 +11391,7 @@
         <v>626</v>
       </c>
       <c r="B108">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -11396,7 +11399,7 @@
         <v>627</v>
       </c>
       <c r="B109">
-        <v>0.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -11404,7 +11407,7 @@
         <v>628</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -11419,8 +11422,16 @@
       <c r="A112" t="s">
         <v>630</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>631</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="641">
   <si>
     <t>id</t>
   </si>
@@ -1201,6 +1201,12 @@
     <t>troop_def_bonus</t>
   </si>
   <si>
+    <t>boon_stat</t>
+  </si>
+  <si>
+    <t>boon_value</t>
+  </si>
+  <si>
     <t>Warden</t>
   </si>
   <si>
@@ -1237,6 +1243,9 @@
     <t>Legendary</t>
   </si>
   <si>
+    <t>worldRevealSpeed</t>
+  </si>
+  <si>
     <t>Adventurer</t>
   </si>
   <si>
@@ -1309,16 +1318,31 @@
     <t>GoldenDragon</t>
   </si>
   <si>
+    <t>unitHp</t>
+  </si>
+  <si>
     <t>VampireLord</t>
   </si>
   <si>
+    <t>heroXp</t>
+  </si>
+  <si>
     <t>Necromancer</t>
   </si>
   <si>
+    <t>researchSpeed</t>
+  </si>
+  <si>
     <t>Pharao</t>
   </si>
   <si>
+    <t>buildSpeed</t>
+  </si>
+  <si>
     <t>ElvenPrincess</t>
+  </si>
+  <si>
+    <t>manaRegen</t>
   </si>
   <si>
     <t>glyph</t>
@@ -7433,7 +7457,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -7446,9 +7470,11 @@
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7494,19 +7520,25 @@
       <c r="O1" s="1" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -7541,19 +7573,25 @@
       <c r="O2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" t="s">
         <v>393</v>
-      </c>
-      <c r="B3" t="s">
-        <v>391</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -7588,19 +7626,25 @@
       <c r="O3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -7635,19 +7679,25 @@
       <c r="O4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" t="s">
         <v>398</v>
-      </c>
-      <c r="B5" t="s">
-        <v>396</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -7682,19 +7732,25 @@
       <c r="O5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -7729,19 +7785,25 @@
       <c r="O6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -7776,19 +7838,25 @@
       <c r="O7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -7823,19 +7891,25 @@
       <c r="O8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -7870,19 +7944,25 @@
       <c r="O9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -7917,19 +7997,25 @@
       <c r="O10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -7964,19 +8050,25 @@
       <c r="O11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8011,19 +8103,25 @@
       <c r="O12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8058,19 +8156,25 @@
       <c r="O13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8105,19 +8209,25 @@
       <c r="O14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8152,19 +8262,25 @@
       <c r="O15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8199,19 +8315,25 @@
       <c r="O16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B17" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8246,19 +8368,25 @@
       <c r="O17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -8293,19 +8421,25 @@
       <c r="O18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B19" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -8340,19 +8474,25 @@
       <c r="O19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B20" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -8387,19 +8527,25 @@
       <c r="O20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -8434,19 +8580,25 @@
       <c r="O21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B22" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -8481,19 +8633,25 @@
       <c r="O22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B23" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -8528,19 +8686,25 @@
       <c r="O23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B24" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -8575,19 +8739,25 @@
       <c r="O24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -8622,19 +8792,25 @@
       <c r="O25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -8669,19 +8845,25 @@
       <c r="O26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -8716,19 +8898,25 @@
       <c r="O27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B28" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -8763,19 +8951,25 @@
       <c r="O28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B29" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -8810,19 +9004,25 @@
       <c r="O29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q29">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B30" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -8857,19 +9057,25 @@
       <c r="O30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q30">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -8904,19 +9110,25 @@
       <c r="O31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -8951,19 +9163,25 @@
       <c r="O32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q32">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B33" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -8997,6 +9215,12 @@
       </c>
       <c r="O33">
         <v>2</v>
+      </c>
+      <c r="P33" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q33">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -9026,10 +9250,10 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>381</v>
@@ -9061,16 +9285,16 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B2" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9102,16 +9326,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9143,16 +9367,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B4" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="D4" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -9184,16 +9408,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B5" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C5" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="D5" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -9225,16 +9449,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D6" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -9295,51 +9519,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -9386,7 +9610,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -9454,27 +9678,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -9497,7 +9721,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -9520,7 +9744,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -9543,7 +9767,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -9566,7 +9790,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -9589,7 +9813,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -9612,7 +9836,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -9635,7 +9859,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -9658,7 +9882,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -9681,7 +9905,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -9725,48 +9949,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -9787,10 +10011,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -9807,7 +10031,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -9828,10 +10052,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -9848,7 +10072,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -9869,10 +10093,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="I4" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -9889,7 +10113,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -9910,10 +10134,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="I5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -9930,7 +10154,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -9951,10 +10175,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="I6" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -9971,7 +10195,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -9992,10 +10216,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="I7" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10012,7 +10236,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10033,10 +10257,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="I8" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10053,7 +10277,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10074,10 +10298,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="I9" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10094,7 +10318,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10115,10 +10339,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="I10" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10135,7 +10359,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10156,10 +10380,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="I11" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -10176,7 +10400,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -10197,10 +10421,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="I12" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -10217,7 +10441,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -10238,10 +10462,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="I13" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -10258,7 +10482,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -10279,10 +10503,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="I14" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -10299,7 +10523,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -10320,10 +10544,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="I15" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -10340,7 +10564,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -10361,10 +10585,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="I16" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -10401,19 +10625,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10532,15 +10756,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10548,7 +10772,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -10556,7 +10780,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -10564,7 +10788,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -10572,15 +10796,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -10588,7 +10812,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -10596,7 +10820,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -10604,7 +10828,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -10612,7 +10836,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -10620,7 +10844,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -10628,7 +10852,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B13">
         <v>1.25</v>
@@ -10636,7 +10860,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -10644,15 +10868,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -10660,7 +10884,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B17">
         <v>1.05</v>
@@ -10668,7 +10892,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -10676,7 +10900,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -10684,7 +10908,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10692,15 +10916,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B22">
         <v>1.05</v>
@@ -10708,7 +10932,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -10716,7 +10940,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -10724,7 +10948,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -10732,7 +10956,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B26">
         <v>2500</v>
@@ -10740,7 +10964,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -10748,7 +10972,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B28">
         <v>0.1</v>
@@ -10756,7 +10980,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -10764,7 +10988,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -10772,7 +10996,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -10780,7 +11004,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B32">
         <v>50</v>
@@ -10788,7 +11012,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B33">
         <v>250</v>
@@ -10796,7 +11020,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B34">
         <v>2000</v>
@@ -10804,7 +11028,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -10812,47 +11036,47 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B41">
         <v>20000</v>
@@ -10860,7 +11084,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -10868,7 +11092,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -10876,7 +11100,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B44">
         <v>2500</v>
@@ -10884,7 +11108,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -10892,7 +11116,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B46">
         <v>100</v>
@@ -10900,7 +11124,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B47">
         <v>12</v>
@@ -10908,23 +11132,23 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -10932,7 +11156,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B51">
         <v>30</v>
@@ -10940,15 +11164,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B53">
         <v>14</v>
@@ -10956,7 +11180,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B54">
         <v>2000</v>
@@ -10964,7 +11188,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B55">
         <v>25000</v>
@@ -10972,31 +11196,31 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B59">
         <v>60</v>
@@ -11004,15 +11228,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -11020,7 +11244,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="B62">
         <v>30</v>
@@ -11028,7 +11252,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B63">
         <v>50</v>
@@ -11036,7 +11260,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B64">
         <v>200</v>
@@ -11044,15 +11268,15 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -11060,7 +11284,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B67">
         <v>24</v>
@@ -11068,7 +11292,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B68">
         <v>10</v>
@@ -11076,7 +11300,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -11084,7 +11308,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="B70">
         <v>10</v>
@@ -11092,7 +11316,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -11100,7 +11324,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B72">
         <v>50</v>
@@ -11108,7 +11332,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -11116,7 +11340,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B74">
         <v>100</v>
@@ -11124,7 +11348,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B75">
         <v>1.09</v>
@@ -11132,7 +11356,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B76">
         <v>10</v>
@@ -11140,7 +11364,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B77">
         <v>50</v>
@@ -11148,7 +11372,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -11156,7 +11380,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="B79">
         <v>0.2</v>
@@ -11164,7 +11388,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -11172,7 +11396,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -11180,7 +11404,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B82">
         <v>0.3</v>
@@ -11188,7 +11412,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="B83">
         <v>1.5</v>
@@ -11196,7 +11420,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B84">
         <v>0.75</v>
@@ -11204,7 +11428,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B85">
         <v>0.4</v>
@@ -11212,7 +11436,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="B86">
         <v>100</v>
@@ -11220,7 +11444,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="B87">
         <v>600</v>
@@ -11228,7 +11452,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -11236,7 +11460,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -11244,7 +11468,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B90">
         <v>3</v>
@@ -11252,7 +11476,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B91">
         <v>4</v>
@@ -11260,7 +11484,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -11268,7 +11492,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="B93">
         <v>6</v>
@@ -11276,7 +11500,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B94">
         <v>400</v>
@@ -11284,7 +11508,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B95">
         <v>0.3</v>
@@ -11292,7 +11516,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -11300,7 +11524,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="B97">
         <v>0.5</v>
@@ -11308,7 +11532,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B98">
         <v>0.1</v>
@@ -11316,7 +11540,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B99">
         <v>0.3</v>
@@ -11324,7 +11548,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="B100">
         <v>0.25</v>
@@ -11332,7 +11556,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B101">
         <v>500</v>
@@ -11340,7 +11564,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="B102">
         <v>15</v>
@@ -11348,7 +11572,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B103">
         <v>150</v>
@@ -11356,7 +11580,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -11364,7 +11588,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -11372,7 +11596,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B106">
         <v>2500</v>
@@ -11380,7 +11604,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -11388,7 +11612,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="B108">
         <v>30</v>
@@ -11396,7 +11620,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B109">
         <v>90</v>
@@ -11404,7 +11628,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B110">
         <v>0.5</v>
@@ -11412,7 +11636,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -11420,7 +11644,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -11428,10 +11652,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -11175,7 +11175,7 @@
         <v>574</v>
       </c>
       <c r="B53">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -7354,10 +7354,10 @@
         <v>375</v>
       </c>
       <c r="B2">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="C2">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -7374,10 +7374,10 @@
         <v>376</v>
       </c>
       <c r="B3">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>-0.05</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -7394,10 +7394,10 @@
         <v>377</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -7420,7 +7420,7 @@
         <v>0.1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2981" uniqueCount="644">
   <si>
     <t>id</t>
   </si>
@@ -1169,6 +1169,15 @@
   </si>
   <si>
     <t>WanderersCompass</t>
+  </si>
+  <si>
+    <t>DelversLantern</t>
+  </si>
+  <si>
+    <t>MusterHorn</t>
+  </si>
+  <si>
+    <t>BailiffsTally</t>
   </si>
   <si>
     <t>rarity</t>
@@ -7318,7 +7327,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7446,6 +7455,66 @@
         <v>31</v>
       </c>
       <c r="F6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7">
+        <v>1.15</v>
+      </c>
+      <c r="C7">
+        <v>0.15</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8">
+        <v>1.1</v>
+      </c>
+      <c r="C8">
+        <v>0.1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9">
+        <v>1.15</v>
+      </c>
+      <c r="C9">
+        <v>0.15</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7479,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -7503,42 +7572,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -7582,16 +7651,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -7635,16 +7704,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -7688,16 +7757,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -7741,16 +7810,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -7786,7 +7855,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -7794,16 +7863,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -7847,16 +7916,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -7900,16 +7969,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -7953,16 +8022,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8006,16 +8075,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8059,16 +8128,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B12" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8112,16 +8181,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8165,16 +8234,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8218,16 +8287,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B15" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8271,16 +8340,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B16" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8324,16 +8393,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B17" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8377,16 +8446,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B18" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -8430,16 +8499,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -8483,16 +8552,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B20" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -8536,16 +8605,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B21" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -8589,16 +8658,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B22" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -8642,16 +8711,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B23" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -8695,16 +8764,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -8748,16 +8817,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B25" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -8801,16 +8870,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B26" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -8854,16 +8923,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B27" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -8907,16 +8976,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B28" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -8960,16 +9029,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9005,7 +9074,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9013,16 +9082,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B30" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9058,7 +9127,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9066,16 +9135,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B31" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9111,7 +9180,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9119,16 +9188,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B32" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9164,7 +9233,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9172,16 +9241,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B33" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9217,7 +9286,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9250,13 +9319,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9274,27 +9343,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9326,16 +9395,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9367,16 +9436,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -9408,16 +9477,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D5" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -9449,16 +9518,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -9519,51 +9588,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -9610,7 +9679,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -9678,27 +9747,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -9721,7 +9790,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -9744,7 +9813,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -9767,7 +9836,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -9790,7 +9859,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -9813,7 +9882,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -9836,7 +9905,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -9859,7 +9928,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -9882,7 +9951,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -9905,7 +9974,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -9949,48 +10018,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10011,10 +10080,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10031,7 +10100,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10052,10 +10121,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10072,7 +10141,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10093,10 +10162,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="I4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10113,7 +10182,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10134,10 +10203,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10154,7 +10223,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10175,10 +10244,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10195,7 +10264,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10216,10 +10285,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10236,7 +10305,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10257,10 +10326,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10277,7 +10346,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10298,10 +10367,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10318,7 +10387,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10339,10 +10408,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10359,7 +10428,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10380,10 +10449,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -10400,7 +10469,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -10421,10 +10490,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -10441,7 +10510,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -10462,10 +10531,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -10482,7 +10551,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -10503,10 +10572,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I14" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -10523,7 +10592,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -10544,10 +10613,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I15" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -10564,7 +10633,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -10585,10 +10654,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I16" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -10625,19 +10694,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10756,15 +10825,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10772,7 +10841,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -10780,7 +10849,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -10788,7 +10857,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -10796,15 +10865,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -10812,7 +10881,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -10820,7 +10889,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -10828,7 +10897,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -10836,7 +10905,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -10844,7 +10913,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -10852,7 +10921,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B13">
         <v>1.25</v>
@@ -10860,7 +10929,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -10868,15 +10937,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -10884,7 +10953,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B17">
         <v>1.05</v>
@@ -10892,7 +10961,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -10900,7 +10969,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -10908,7 +10977,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10916,15 +10985,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B22">
         <v>1.05</v>
@@ -10932,7 +11001,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -10940,7 +11009,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -10948,7 +11017,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -10956,7 +11025,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B26">
         <v>2500</v>
@@ -10964,7 +11033,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -10972,7 +11041,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B28">
         <v>0.1</v>
@@ -10980,7 +11049,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -10988,7 +11057,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -10996,7 +11065,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -11004,7 +11073,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B32">
         <v>50</v>
@@ -11012,7 +11081,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B33">
         <v>250</v>
@@ -11020,7 +11089,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B34">
         <v>2000</v>
@@ -11028,7 +11097,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -11036,47 +11105,47 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B41">
         <v>20000</v>
@@ -11084,7 +11153,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -11092,7 +11161,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -11100,7 +11169,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B44">
         <v>2500</v>
@@ -11108,7 +11177,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -11116,7 +11185,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B46">
         <v>100</v>
@@ -11124,7 +11193,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B47">
         <v>12</v>
@@ -11132,23 +11201,23 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -11156,7 +11225,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B51">
         <v>30</v>
@@ -11164,15 +11233,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B53">
         <v>28</v>
@@ -11180,7 +11249,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B54">
         <v>2000</v>
@@ -11188,7 +11257,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B55">
         <v>25000</v>
@@ -11196,31 +11265,31 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B59">
         <v>60</v>
@@ -11228,15 +11297,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -11244,7 +11313,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B62">
         <v>30</v>
@@ -11252,7 +11321,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B63">
         <v>50</v>
@@ -11260,7 +11329,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B64">
         <v>200</v>
@@ -11268,15 +11337,15 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -11284,7 +11353,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B67">
         <v>24</v>
@@ -11292,7 +11361,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B68">
         <v>10</v>
@@ -11300,7 +11369,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -11308,7 +11377,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B70">
         <v>10</v>
@@ -11316,7 +11385,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -11324,7 +11393,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B72">
         <v>50</v>
@@ -11332,7 +11401,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -11340,7 +11409,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B74">
         <v>100</v>
@@ -11348,7 +11417,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B75">
         <v>1.09</v>
@@ -11356,7 +11425,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B76">
         <v>10</v>
@@ -11364,7 +11433,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B77">
         <v>50</v>
@@ -11372,7 +11441,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -11380,7 +11449,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B79">
         <v>0.2</v>
@@ -11388,7 +11457,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -11396,7 +11465,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -11404,7 +11473,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B82">
         <v>0.3</v>
@@ -11412,7 +11481,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B83">
         <v>1.5</v>
@@ -11420,7 +11489,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B84">
         <v>0.75</v>
@@ -11428,7 +11497,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B85">
         <v>0.4</v>
@@ -11436,7 +11505,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B86">
         <v>100</v>
@@ -11444,7 +11513,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B87">
         <v>600</v>
@@ -11452,7 +11521,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -11460,7 +11529,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -11468,7 +11537,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B90">
         <v>3</v>
@@ -11476,7 +11545,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B91">
         <v>4</v>
@@ -11484,7 +11553,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -11492,7 +11561,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B93">
         <v>6</v>
@@ -11500,7 +11569,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B94">
         <v>400</v>
@@ -11508,7 +11577,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B95">
         <v>0.3</v>
@@ -11516,7 +11585,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -11524,7 +11593,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B97">
         <v>0.5</v>
@@ -11532,7 +11601,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B98">
         <v>0.1</v>
@@ -11540,7 +11609,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B99">
         <v>0.3</v>
@@ -11548,7 +11617,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B100">
         <v>0.25</v>
@@ -11556,7 +11625,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B101">
         <v>500</v>
@@ -11564,7 +11633,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B102">
         <v>15</v>
@@ -11572,7 +11641,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B103">
         <v>150</v>
@@ -11580,7 +11649,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -11588,7 +11657,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -11596,7 +11665,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B106">
         <v>2500</v>
@@ -11604,7 +11673,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -11612,7 +11681,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B108">
         <v>30</v>
@@ -11620,7 +11689,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B109">
         <v>90</v>
@@ -11628,7 +11697,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B110">
         <v>0.5</v>
@@ -11636,7 +11705,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -11644,7 +11713,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -11652,10 +11721,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2981" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="656">
   <si>
     <t>id</t>
   </si>
@@ -1108,6 +1108,27 @@
     <t>cards</t>
   </si>
   <si>
+    <t>guarantee_1star</t>
+  </si>
+  <si>
+    <t>guarantee_2star</t>
+  </si>
+  <si>
+    <t>guarantee_3star</t>
+  </si>
+  <si>
+    <t>guarantee_4star</t>
+  </si>
+  <si>
+    <t>guarantee_5star</t>
+  </si>
+  <si>
+    <t>guarantee_4gold</t>
+  </si>
+  <si>
+    <t>guarantee_5gold</t>
+  </si>
+  <si>
     <t>weight_1star</t>
   </si>
   <si>
@@ -1123,22 +1144,40 @@
     <t>weight_5star</t>
   </si>
   <si>
-    <t>gold_chance</t>
-  </si>
-  <si>
-    <t>gold_guaranteed</t>
+    <t>weight_4gold</t>
+  </si>
+  <si>
+    <t>weight_5gold</t>
   </si>
   <si>
     <t>gem_cost</t>
   </si>
   <si>
-    <t>Bronze</t>
-  </si>
-  <si>
-    <t>Silver</t>
-  </si>
-  <si>
-    <t>Star</t>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Golden</t>
+  </si>
+  <si>
+    <t>BronzeChest</t>
+  </si>
+  <si>
+    <t>SilverChest</t>
+  </si>
+  <si>
+    <t>GoldChest</t>
   </si>
   <si>
     <t>passive_base</t>
@@ -1792,22 +1831,19 @@
     <t>collection.chest_floor_per_hour</t>
   </si>
   <si>
-    <t>collection.stars_per_rarity</t>
-  </si>
-  <si>
-    <t>1,2,5,10,25</t>
-  </si>
-  <si>
-    <t>collection.star_gold_multiplier</t>
+    <t>collection.stars_per_face</t>
+  </si>
+  <si>
+    <t>1star:2,2star:6,3star:16,4star:40,5star:100,4gold:80,5gold:200</t>
   </si>
   <si>
     <t>collection.close_gold_seconds_per_star</t>
   </si>
   <si>
-    <t>collection.vault_gold_stars</t>
-  </si>
-  <si>
-    <t>collection.vault_star_stars</t>
+    <t>collection.chest_stars</t>
+  </si>
+  <si>
+    <t>BronzeChest:105,SilverChest:250,GoldChest:400</t>
   </si>
   <si>
     <t>collection.wildcard_gem_costs</t>
@@ -7149,17 +7185,16 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="3" max="9" width="17" customWidth="1"/>
+    <col min="10" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7190,133 +7225,503 @@
       <c r="J1" s="1" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>84.92</v>
+      </c>
+      <c r="K2">
+        <v>12.005</v>
+      </c>
+      <c r="L2">
+        <v>2.5</v>
+      </c>
+      <c r="M2">
+        <v>0.4</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+      <c r="O2">
+        <v>0.06</v>
+      </c>
+      <c r="P2">
+        <v>0.015</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B3">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>70</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B3">
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3">
+        <v>69.85</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>45</v>
-      </c>
-      <c r="D3">
+      <c r="M3">
+        <v>0.8</v>
+      </c>
+      <c r="N3">
+        <v>0.2</v>
+      </c>
+      <c r="O3">
+        <v>0.12</v>
+      </c>
+      <c r="P3">
+        <v>0.03</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>59.8</v>
+      </c>
+      <c r="K4">
+        <v>29.9</v>
+      </c>
+      <c r="L4">
+        <v>8</v>
+      </c>
+      <c r="M4">
+        <v>1.5</v>
+      </c>
+      <c r="N4">
+        <v>0.5</v>
+      </c>
+      <c r="O4">
+        <v>0.225</v>
+      </c>
+      <c r="P4">
+        <v>0.075</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="K5">
         <v>35</v>
       </c>
-      <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4">
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>1.2</v>
+      </c>
+      <c r="O5">
+        <v>0.55</v>
+      </c>
+      <c r="P5">
+        <v>0.25</v>
+      </c>
+      <c r="Q5">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6">
         <v>40</v>
       </c>
-      <c r="E4">
-        <v>38</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4">
-        <v>0.08</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>369</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5">
-        <v>55</v>
-      </c>
-      <c r="F5">
-        <v>33</v>
-      </c>
-      <c r="G5">
+      <c r="K6">
+        <v>34</v>
+      </c>
+      <c r="L6">
+        <v>14.5</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>1.05</v>
+      </c>
+      <c r="P6">
+        <v>0.45</v>
+      </c>
+      <c r="Q6">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7">
+        <v>75</v>
+      </c>
+      <c r="P7">
+        <v>25</v>
+      </c>
+      <c r="Q7">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>84.92</v>
+      </c>
+      <c r="K8">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>0.2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1500</v>
+      <c r="L8">
+        <v>2.5</v>
+      </c>
+      <c r="M8">
+        <v>0.4</v>
+      </c>
+      <c r="N8">
+        <v>0.105</v>
+      </c>
+      <c r="O8">
+        <v>0.06</v>
+      </c>
+      <c r="P8">
+        <v>0.015</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9">
+        <v>59.8</v>
+      </c>
+      <c r="K9">
+        <v>29.9</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>1.5</v>
+      </c>
+      <c r="N9">
+        <v>0.5</v>
+      </c>
+      <c r="O9">
+        <v>0.225</v>
+      </c>
+      <c r="P9">
+        <v>0.075</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10">
+        <v>75</v>
+      </c>
+      <c r="P10">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -7343,24 +7748,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -7380,7 +7785,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7400,7 +7805,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -7420,7 +7825,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -7440,7 +7845,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -7460,7 +7865,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -7480,7 +7885,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -7500,7 +7905,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -7548,16 +7953,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -7572,42 +7977,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -7651,16 +8056,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B3" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -7704,16 +8109,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B4" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -7757,16 +8162,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -7810,16 +8215,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -7855,7 +8260,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -7863,16 +8268,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -7916,16 +8321,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" t="s">
         <v>409</v>
-      </c>
-      <c r="B8" t="s">
-        <v>396</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -7969,16 +8374,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8022,16 +8427,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B10" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8075,16 +8480,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="B11" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8128,16 +8533,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B12" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8181,16 +8586,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B13" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8234,16 +8639,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="B14" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8287,16 +8692,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="B15" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8340,16 +8745,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B16" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8393,16 +8798,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="B17" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8446,16 +8851,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="B18" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -8499,16 +8904,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B19" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -8552,16 +8957,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B20" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -8605,16 +9010,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="B21" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -8658,16 +9063,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="B22" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -8711,16 +9116,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="B23" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -8764,16 +9169,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="B24" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -8817,16 +9222,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="B25" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -8870,16 +9275,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="B26" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -8923,16 +9328,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B27" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -8976,16 +9381,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="B28" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9029,16 +9434,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="B29" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9074,7 +9479,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9082,16 +9487,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="B30" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9127,7 +9532,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9135,16 +9540,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="B31" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9180,7 +9585,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9188,16 +9593,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="B32" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9233,7 +9638,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9241,16 +9646,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="B33" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9286,7 +9691,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9319,13 +9724,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9343,27 +9748,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C2" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="D2" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9395,16 +9800,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="D3" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9436,16 +9841,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B4" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="C4" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="D4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -9477,16 +9882,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="B5" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="C5" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -9518,16 +9923,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="B6" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D6" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -9588,51 +9993,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -9679,7 +10084,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -9747,27 +10152,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -9790,7 +10195,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -9813,7 +10218,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -9836,7 +10241,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -9859,7 +10264,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -9882,7 +10287,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -9905,7 +10310,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -9928,7 +10333,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -9940,7 +10345,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -9951,7 +10356,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -9963,7 +10368,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -9974,7 +10379,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -9986,7 +10391,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -10018,48 +10423,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10080,10 +10485,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="I2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10100,7 +10505,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10121,10 +10526,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="I3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10141,7 +10546,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10162,10 +10567,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="I4" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10182,7 +10587,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10203,10 +10608,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="I5" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10223,7 +10628,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10244,10 +10649,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="I6" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10264,7 +10669,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10285,10 +10690,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="I7" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10305,7 +10710,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10326,10 +10731,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="I8" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10346,7 +10751,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10367,10 +10772,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="I9" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10387,7 +10792,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10408,10 +10813,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="I10" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10428,7 +10833,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10449,10 +10854,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="I11" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -10469,7 +10874,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -10490,10 +10895,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="I12" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -10510,7 +10915,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -10531,10 +10936,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="I13" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -10551,7 +10956,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -10572,10 +10977,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="I14" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -10592,7 +10997,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -10613,10 +11018,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="I15" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -10633,7 +11038,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -10654,10 +11059,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="I16" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -10694,19 +11099,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10817,7 +11222,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -10825,15 +11230,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10841,7 +11246,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -10849,7 +11254,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -10857,7 +11262,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -10865,15 +11270,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -10881,7 +11286,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -10889,7 +11294,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -10897,7 +11302,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -10905,7 +11310,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -10913,7 +11318,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -10921,7 +11326,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="B13">
         <v>1.25</v>
@@ -10929,7 +11334,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -10937,15 +11342,15 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="B16">
         <v>10</v>
@@ -10953,7 +11358,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="B17">
         <v>1.05</v>
@@ -10961,7 +11366,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -10969,7 +11374,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -10977,7 +11382,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -10985,15 +11390,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="B22">
         <v>1.05</v>
@@ -11001,7 +11406,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -11009,7 +11414,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -11017,7 +11422,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -11025,7 +11430,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="B26">
         <v>2500</v>
@@ -11033,7 +11438,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -11041,7 +11446,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="B28">
         <v>0.1</v>
@@ -11049,7 +11454,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -11057,7 +11462,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -11065,7 +11470,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -11073,7 +11478,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="B32">
         <v>50</v>
@@ -11081,7 +11486,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B33">
         <v>250</v>
@@ -11089,7 +11494,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="B34">
         <v>2000</v>
@@ -11097,7 +11502,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="B35">
         <v>20</v>
@@ -11105,47 +11510,47 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="B41">
         <v>20000</v>
@@ -11153,7 +11558,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -11161,7 +11566,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -11169,7 +11574,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="B44">
         <v>2500</v>
@@ -11177,7 +11582,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -11185,7 +11590,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B46">
         <v>100</v>
@@ -11193,7 +11598,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B47">
         <v>12</v>
@@ -11201,23 +11606,23 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="B50">
         <v>10</v>
@@ -11225,7 +11630,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="B51">
         <v>30</v>
@@ -11233,15 +11638,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="B53">
         <v>28</v>
@@ -11249,7 +11654,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B54">
         <v>2000</v>
@@ -11257,7 +11662,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B55">
         <v>25000</v>
@@ -11265,31 +11670,31 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B59">
         <v>60</v>
@@ -11297,71 +11702,71 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>590</v>
-      </c>
-      <c r="B62">
-        <v>30</v>
+        <v>603</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>591</v>
-      </c>
-      <c r="B63">
-        <v>50</v>
+        <v>605</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B64">
-        <v>200</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>593</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>594</v>
+        <v>608</v>
+      </c>
+      <c r="B65">
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B67">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B68">
         <v>10</v>
@@ -11369,23 +11774,23 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B70">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -11393,135 +11798,135 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="B72">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B74">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="B75">
-        <v>1.09</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B77">
-        <v>50</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B79">
-        <v>0.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="B80">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="B82">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="B83">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="B84">
-        <v>0.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="B85">
-        <v>0.4</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="B86">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="B87">
-        <v>600</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -11529,202 +11934,186 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="B94">
-        <v>400</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="B95">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="B97">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="B98">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="B99">
-        <v>0.3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="B100">
-        <v>0.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="B101">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="B102">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="B103">
-        <v>150</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="B104">
-        <v>6</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="B106">
-        <v>2500</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="B108">
-        <v>30</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="B109">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="B110">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>640</v>
-      </c>
-      <c r="B111">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>641</v>
-      </c>
-      <c r="B112">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>642</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>643</v>
+        <v>654</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1813,19 +1813,19 @@
     <t>collection.album_hours</t>
   </si>
   <si>
-    <t>2,2,4,8,8</t>
+    <t>2,2,4,4,6,8,8,8</t>
   </si>
   <si>
     <t>collection.album_silver_keys</t>
   </si>
   <si>
-    <t>1,1,1,0,0</t>
+    <t>1,1,1,1,1,0,0,0</t>
   </si>
   <si>
     <t>collection.album_gold_keys</t>
   </si>
   <si>
-    <t>0,0,0,1,1</t>
+    <t>0,0,0,0,0,1,1,1</t>
   </si>
   <si>
     <t>collection.chest_floor_per_hour</t>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="657">
   <si>
     <t>id</t>
   </si>
@@ -1643,6 +1643,9 @@
   </si>
   <si>
     <t>offline_cap_hours</t>
+  </si>
+  <si>
+    <t>artifacts.active_cooldown_seconds</t>
   </si>
   <si>
     <t>fog.taps_to_reveal</t>
@@ -11222,7 +11225,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -11313,7 +11316,7 @@
         <v>538</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -11321,7 +11324,7 @@
         <v>539</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -11329,7 +11332,7 @@
         <v>540</v>
       </c>
       <c r="B13">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -11337,23 +11340,23 @@
         <v>541</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>542</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>543</v>
+      <c r="B15">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>543</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -11361,7 +11364,7 @@
         <v>545</v>
       </c>
       <c r="B17">
-        <v>1.05</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -11369,7 +11372,7 @@
         <v>546</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -11377,7 +11380,7 @@
         <v>547</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -11385,23 +11388,23 @@
         <v>548</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>549</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>550</v>
+      <c r="B21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>550</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B22">
-        <v>1.05</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -11409,7 +11412,7 @@
         <v>552</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -11417,7 +11420,7 @@
         <v>553</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -11425,7 +11428,7 @@
         <v>554</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -11433,7 +11436,7 @@
         <v>555</v>
       </c>
       <c r="B26">
-        <v>2500</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -11441,7 +11444,7 @@
         <v>556</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -11449,7 +11452,7 @@
         <v>557</v>
       </c>
       <c r="B28">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -11457,7 +11460,7 @@
         <v>558</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -11465,7 +11468,7 @@
         <v>559</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -11473,7 +11476,7 @@
         <v>560</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -11481,7 +11484,7 @@
         <v>561</v>
       </c>
       <c r="B32">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -11489,7 +11492,7 @@
         <v>562</v>
       </c>
       <c r="B33">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -11497,7 +11500,7 @@
         <v>563</v>
       </c>
       <c r="B34">
-        <v>2000</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -11505,55 +11508,55 @@
         <v>564</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>565</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>566</v>
+      <c r="B36">
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>566</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>568</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>570</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>572</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>574</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B41">
-        <v>20000</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -11561,7 +11564,7 @@
         <v>576</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -11569,7 +11572,7 @@
         <v>577</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -11577,7 +11580,7 @@
         <v>578</v>
       </c>
       <c r="B44">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -11585,7 +11588,7 @@
         <v>579</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -11593,7 +11596,7 @@
         <v>580</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -11601,31 +11604,31 @@
         <v>581</v>
       </c>
       <c r="B47">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>582</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>583</v>
+      <c r="B48">
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>583</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>585</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B50">
-        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -11633,23 +11636,23 @@
         <v>587</v>
       </c>
       <c r="B51">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>588</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>589</v>
+      <c r="B52">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>589</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="B53">
-        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -11657,7 +11660,7 @@
         <v>591</v>
       </c>
       <c r="B54">
-        <v>2000</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -11665,79 +11668,79 @@
         <v>592</v>
       </c>
       <c r="B55">
-        <v>25000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>593</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>594</v>
+      <c r="B56">
+        <v>25000</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>594</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>596</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>598</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B59">
-        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>600</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>601</v>
+      <c r="B60">
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>601</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="B61">
-        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>603</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>604</v>
+      <c r="B62">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>604</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>606</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -11745,7 +11748,7 @@
         <v>608</v>
       </c>
       <c r="B65">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -11753,7 +11756,7 @@
         <v>609</v>
       </c>
       <c r="B66">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -11761,7 +11764,7 @@
         <v>610</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -11769,7 +11772,7 @@
         <v>611</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -11777,7 +11780,7 @@
         <v>612</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -11785,7 +11788,7 @@
         <v>613</v>
       </c>
       <c r="B70">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -11793,7 +11796,7 @@
         <v>614</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -11801,7 +11804,7 @@
         <v>615</v>
       </c>
       <c r="B72">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -11809,7 +11812,7 @@
         <v>616</v>
       </c>
       <c r="B73">
-        <v>1.09</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -11817,7 +11820,7 @@
         <v>617</v>
       </c>
       <c r="B74">
-        <v>10</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -11825,7 +11828,7 @@
         <v>618</v>
       </c>
       <c r="B75">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -11833,7 +11836,7 @@
         <v>619</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -11841,7 +11844,7 @@
         <v>620</v>
       </c>
       <c r="B77">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -11857,7 +11860,7 @@
         <v>622</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -11865,7 +11868,7 @@
         <v>623</v>
       </c>
       <c r="B80">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -11873,7 +11876,7 @@
         <v>624</v>
       </c>
       <c r="B81">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -11881,7 +11884,7 @@
         <v>625</v>
       </c>
       <c r="B82">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -11889,7 +11892,7 @@
         <v>626</v>
       </c>
       <c r="B83">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -11897,7 +11900,7 @@
         <v>627</v>
       </c>
       <c r="B84">
-        <v>100</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -11905,7 +11908,7 @@
         <v>628</v>
       </c>
       <c r="B85">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -11913,7 +11916,7 @@
         <v>629</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -11921,7 +11924,7 @@
         <v>630</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -11929,7 +11932,7 @@
         <v>631</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -11937,7 +11940,7 @@
         <v>632</v>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -11945,7 +11948,7 @@
         <v>633</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -11953,7 +11956,7 @@
         <v>634</v>
       </c>
       <c r="B91">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -11961,7 +11964,7 @@
         <v>635</v>
       </c>
       <c r="B92">
-        <v>400</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -11969,7 +11972,7 @@
         <v>636</v>
       </c>
       <c r="B93">
-        <v>0.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -11977,7 +11980,7 @@
         <v>637</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -11985,7 +11988,7 @@
         <v>638</v>
       </c>
       <c r="B95">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -11993,7 +11996,7 @@
         <v>639</v>
       </c>
       <c r="B96">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -12001,7 +12004,7 @@
         <v>640</v>
       </c>
       <c r="B97">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -12009,7 +12012,7 @@
         <v>641</v>
       </c>
       <c r="B98">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -12017,7 +12020,7 @@
         <v>642</v>
       </c>
       <c r="B99">
-        <v>500</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -12025,7 +12028,7 @@
         <v>643</v>
       </c>
       <c r="B100">
-        <v>15</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -12033,7 +12036,7 @@
         <v>644</v>
       </c>
       <c r="B101">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -12041,7 +12044,7 @@
         <v>645</v>
       </c>
       <c r="B102">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -12049,7 +12052,7 @@
         <v>646</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -12057,7 +12060,7 @@
         <v>647</v>
       </c>
       <c r="B104">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -12065,7 +12068,7 @@
         <v>648</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -12073,7 +12076,7 @@
         <v>649</v>
       </c>
       <c r="B106">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -12081,7 +12084,7 @@
         <v>650</v>
       </c>
       <c r="B107">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -12089,7 +12092,7 @@
         <v>651</v>
       </c>
       <c r="B108">
-        <v>0.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -12097,7 +12100,7 @@
         <v>652</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -12112,8 +12115,16 @@
       <c r="A111" t="s">
         <v>654</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>655</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="659">
   <si>
     <t>id</t>
   </si>
@@ -1646,6 +1646,12 @@
   </si>
   <si>
     <t>artifacts.active_cooldown_seconds</t>
+  </si>
+  <si>
+    <t>artifacts.active_radius_steps</t>
+  </si>
+  <si>
+    <t>5,10,20</t>
   </si>
   <si>
     <t>fog.taps_to_reveal</t>
@@ -11225,7 +11231,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -11323,208 +11329,208 @@
       <c r="A12" t="s">
         <v>539</v>
       </c>
-      <c r="B12">
-        <v>5</v>
+      <c r="B12" s="2" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B14">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>543</v>
-      </c>
-      <c r="B16" s="2" t="s">
         <v>544</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>545</v>
       </c>
-      <c r="B17">
-        <v>10</v>
+      <c r="B17" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B18">
-        <v>1.05</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>550</v>
-      </c>
-      <c r="B22" s="2" t="s">
         <v>551</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>552</v>
       </c>
-      <c r="B23">
-        <v>1.05</v>
+      <c r="B23" s="2" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B27">
-        <v>2500</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B29">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B33">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B34">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B35">
-        <v>2000</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>566</v>
-      </c>
-      <c r="B37" s="2" t="s">
         <v>567</v>
+      </c>
+      <c r="B37">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -11563,64 +11569,64 @@
       <c r="A42" t="s">
         <v>576</v>
       </c>
-      <c r="B42">
-        <v>20000</v>
+      <c r="B42" s="2" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B45">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B47">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>583</v>
-      </c>
-      <c r="B49" s="2" t="s">
         <v>584</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -11635,56 +11641,56 @@
       <c r="A51" t="s">
         <v>587</v>
       </c>
-      <c r="B51">
-        <v>10</v>
+      <c r="B51" s="2" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B52">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>589</v>
-      </c>
-      <c r="B53" s="2" t="s">
         <v>590</v>
+      </c>
+      <c r="B53">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>591</v>
       </c>
-      <c r="B54">
-        <v>28</v>
+      <c r="B54" s="2" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B55">
-        <v>2000</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B56">
-        <v>25000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>594</v>
-      </c>
-      <c r="B57" s="2" t="s">
         <v>595</v>
+      </c>
+      <c r="B57">
+        <v>25000</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -11707,32 +11713,32 @@
       <c r="A60" t="s">
         <v>600</v>
       </c>
-      <c r="B60">
-        <v>60</v>
+      <c r="B60" s="2" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>601</v>
-      </c>
-      <c r="B61" s="2" t="s">
         <v>602</v>
+      </c>
+      <c r="B61">
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>603</v>
       </c>
-      <c r="B62">
-        <v>30</v>
+      <c r="B62" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>604</v>
-      </c>
-      <c r="B63" s="2" t="s">
         <v>605</v>
+      </c>
+      <c r="B63">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -11747,117 +11753,117 @@
       <c r="A65" t="s">
         <v>608</v>
       </c>
-      <c r="B65">
-        <v>3</v>
+      <c r="B65" s="2" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B66">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B67">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B69">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B71">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B73">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B74">
-        <v>1.09</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B75">
-        <v>10</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B76">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B78">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B79">
         <v>0.2</v>
@@ -11865,255 +11871,255 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B80">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B81">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B82">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B83">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B84">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B85">
-        <v>100</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B86">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B92">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B93">
-        <v>400</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B94">
-        <v>0.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B96">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B97">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B98">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B99">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B100">
-        <v>500</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B102">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B103">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B105">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B107">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B108">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B109">
-        <v>0.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -12121,10 +12127,18 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>655</v>
-      </c>
-      <c r="B112" s="2" t="s">
         <v>656</v>
+      </c>
+      <c r="B112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>657</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3047" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="662">
   <si>
     <t>id</t>
   </si>
@@ -1195,6 +1195,12 @@
     <t>active_radius</t>
   </si>
   <si>
+    <t>active_taps_per_mana</t>
+  </si>
+  <si>
+    <t>active_taps_per_mana_per_level</t>
+  </si>
+  <si>
     <t>DowsingRod</t>
   </si>
   <si>
@@ -1652,6 +1658,9 @@
   </si>
   <si>
     <t>5,10,20</t>
+  </si>
+  <si>
+    <t>artifacts.auto_tap_per_second</t>
   </si>
   <si>
     <t>fog.taps_to_reveal</t>
@@ -7741,7 +7750,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7750,9 +7759,11 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7771,10 +7782,16 @@
       <c r="F1" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -7791,10 +7808,16 @@
       <c r="F2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7811,10 +7834,16 @@
       <c r="F3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -7831,10 +7860,16 @@
       <c r="F4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -7851,10 +7886,16 @@
       <c r="F5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -7871,10 +7912,16 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -7891,10 +7938,16 @@
       <c r="F7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -7911,10 +7964,16 @@
       <c r="F8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -7929,6 +7988,12 @@
         <v>31</v>
       </c>
       <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7962,16 +8027,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -7986,42 +8051,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -8065,16 +8130,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B3" t="s">
         <v>411</v>
-      </c>
-      <c r="B3" t="s">
-        <v>409</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -8118,16 +8183,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -8171,16 +8236,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B5" t="s">
         <v>416</v>
-      </c>
-      <c r="B5" t="s">
-        <v>414</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -8224,16 +8289,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -8269,7 +8334,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -8277,16 +8342,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -8330,16 +8395,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -8383,16 +8448,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8436,16 +8501,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8489,16 +8554,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8542,16 +8607,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8595,16 +8660,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B13" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8648,16 +8713,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8701,16 +8766,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8754,16 +8819,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8807,16 +8872,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8860,16 +8925,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B18" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -8913,16 +8978,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -8966,16 +9031,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B20" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -9019,16 +9084,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B21" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -9072,16 +9137,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B22" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -9125,16 +9190,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -9178,16 +9243,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B24" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -9231,16 +9296,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B25" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -9284,16 +9349,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B26" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -9337,16 +9402,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B27" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -9390,16 +9455,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9443,16 +9508,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B29" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9488,7 +9553,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9496,16 +9561,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9541,7 +9606,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9549,16 +9614,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9594,7 +9659,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9602,16 +9667,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B32" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9647,7 +9712,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9655,16 +9720,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B33" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9700,7 +9765,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9733,13 +9798,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9757,27 +9822,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9809,16 +9874,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9850,16 +9915,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -9891,16 +9956,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -9932,16 +9997,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -10002,51 +10067,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -10093,7 +10158,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -10161,27 +10226,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -10204,7 +10269,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -10227,7 +10292,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -10250,7 +10315,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -10273,7 +10338,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -10296,7 +10361,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -10319,7 +10384,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -10342,7 +10407,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -10365,7 +10430,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -10388,7 +10453,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -10432,48 +10497,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10494,10 +10559,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10514,7 +10579,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10535,10 +10600,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10555,7 +10620,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10576,10 +10641,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10596,7 +10661,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10617,10 +10682,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10637,7 +10702,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10658,10 +10723,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10678,7 +10743,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10699,10 +10764,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10719,7 +10784,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10740,10 +10805,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10760,7 +10825,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10781,10 +10846,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10801,7 +10866,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10822,10 +10887,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10842,7 +10907,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10863,10 +10928,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -10883,7 +10948,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -10904,10 +10969,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -10924,7 +10989,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -10945,10 +11010,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -10965,7 +11030,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -10986,10 +11051,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -11006,7 +11071,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11027,10 +11092,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I15" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -11047,7 +11112,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11068,10 +11133,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -11108,19 +11173,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11231,7 +11296,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -11239,15 +11304,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11255,7 +11320,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11263,7 +11328,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11271,7 +11336,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11279,15 +11344,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11295,7 +11360,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11303,7 +11368,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11311,7 +11376,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11319,7 +11384,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11327,551 +11392,551 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B15">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>545</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>547</v>
-      </c>
-      <c r="B18">
-        <v>10</v>
+        <v>548</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B19">
-        <v>1.05</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>552</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>554</v>
-      </c>
-      <c r="B24">
-        <v>1.05</v>
+        <v>555</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B28">
-        <v>2500</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B30">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B34">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B35">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B36">
-        <v>2000</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>568</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
+      </c>
+      <c r="B38">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>578</v>
-      </c>
-      <c r="B43">
-        <v>20000</v>
+        <v>579</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B46">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B48">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B49">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>585</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>589</v>
-      </c>
-      <c r="B52">
-        <v>10</v>
+        <v>590</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B53">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>591</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
+      </c>
+      <c r="B54">
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>593</v>
-      </c>
-      <c r="B55">
-        <v>28</v>
+        <v>594</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B56">
-        <v>2000</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B57">
-        <v>25000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>596</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
+      </c>
+      <c r="B58">
+        <v>25000</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>602</v>
-      </c>
-      <c r="B61">
-        <v>60</v>
+        <v>603</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>603</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
+      </c>
+      <c r="B62">
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>605</v>
-      </c>
-      <c r="B63">
-        <v>30</v>
+        <v>606</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>606</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
+      </c>
+      <c r="B64">
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>610</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
+        <v>611</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B67">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B68">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B70">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B72">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B74">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B75">
-        <v>1.09</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B76">
-        <v>10</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B77">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B79">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -11879,255 +11944,255 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B82">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B83">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B84">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B85">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B86">
-        <v>100</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B87">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B94">
-        <v>400</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B95">
-        <v>0.3</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B97">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B98">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B99">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B100">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B101">
-        <v>500</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B102">
-        <v>15</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B103">
-        <v>150</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B104">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B106">
-        <v>2500</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B108">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B109">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B110">
-        <v>0.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -12135,10 +12200,18 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>657</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
+      </c>
+      <c r="B113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>660</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>661</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3076" uniqueCount="664">
   <si>
     <t>id</t>
   </si>
@@ -1199,6 +1199,12 @@
   </si>
   <si>
     <t>active_taps_per_mana_per_level</t>
+  </si>
+  <si>
+    <t>active_power</t>
+  </si>
+  <si>
+    <t>active_power_per_level</t>
   </si>
   <si>
     <t>DowsingRod</t>
@@ -7750,7 +7756,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7761,9 +7767,11 @@
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,10 +7796,16 @@
       <c r="H1" s="1" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -7814,10 +7828,16 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7840,10 +7860,16 @@
       <c r="H3">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -7855,10 +7881,10 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>3600</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
+        <v>300</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
@@ -7866,10 +7892,16 @@
       <c r="H4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -7878,24 +7910,30 @@
         <v>0.1</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>0.25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -7918,10 +7956,16 @@
       <c r="H6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -7944,10 +7988,16 @@
       <c r="H7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -7970,10 +8020,16 @@
       <c r="H8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -7994,6 +8050,12 @@
         <v>31</v>
       </c>
       <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8027,16 +8089,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -8051,42 +8113,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -8130,16 +8192,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B3" t="s">
         <v>413</v>
-      </c>
-      <c r="B3" t="s">
-        <v>411</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -8183,16 +8245,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -8236,16 +8298,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" t="s">
         <v>418</v>
-      </c>
-      <c r="B5" t="s">
-        <v>416</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -8289,16 +8351,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -8334,7 +8396,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -8342,16 +8404,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -8395,16 +8457,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -8448,16 +8510,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8501,16 +8563,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8554,16 +8616,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8607,16 +8669,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B12" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8660,16 +8722,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8713,16 +8775,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8766,16 +8828,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8819,16 +8881,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B16" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8872,16 +8934,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8925,16 +8987,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -8978,16 +9040,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B19" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -9031,16 +9093,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -9084,16 +9146,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B21" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -9137,16 +9199,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B22" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -9190,16 +9252,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B23" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -9243,16 +9305,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B24" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -9296,16 +9358,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B25" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -9349,16 +9411,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B26" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -9402,16 +9464,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B27" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -9455,16 +9517,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B28" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9508,16 +9570,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9553,7 +9615,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9561,16 +9623,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9606,7 +9668,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9614,16 +9676,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9659,7 +9721,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9667,16 +9729,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9712,7 +9774,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9720,16 +9782,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B33" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9765,7 +9827,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9798,13 +9860,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9822,27 +9884,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9874,16 +9936,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9915,16 +9977,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -9956,16 +10018,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -9997,16 +10059,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -10067,51 +10129,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -10158,7 +10220,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -10226,27 +10288,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -10269,7 +10331,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -10292,7 +10354,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -10315,7 +10377,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -10338,7 +10400,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -10361,7 +10423,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -10384,7 +10446,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -10407,7 +10469,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -10430,7 +10492,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -10453,7 +10515,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -10497,48 +10559,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10559,10 +10621,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10579,7 +10641,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10600,10 +10662,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10620,7 +10682,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10641,10 +10703,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10661,7 +10723,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10682,10 +10744,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10702,7 +10764,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10723,10 +10785,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10743,7 +10805,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10764,10 +10826,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10784,7 +10846,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10805,10 +10867,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10825,7 +10887,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10846,10 +10908,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10866,7 +10928,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10887,10 +10949,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10907,7 +10969,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10928,10 +10990,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -10948,7 +11010,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -10969,10 +11031,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I12" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -10989,7 +11051,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11010,10 +11072,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -11030,7 +11092,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11051,10 +11113,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -11071,7 +11133,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11092,10 +11154,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -11112,7 +11174,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11133,10 +11195,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -11173,19 +11235,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11304,15 +11366,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11320,7 +11382,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11328,7 +11390,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11336,7 +11398,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11344,15 +11406,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11360,7 +11422,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11368,7 +11430,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11376,7 +11438,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11384,7 +11446,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11392,15 +11454,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -11408,7 +11470,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -11416,7 +11478,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11424,7 +11486,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B16">
         <v>1.25</v>
@@ -11432,7 +11494,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -11440,15 +11502,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -11456,7 +11518,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B20">
         <v>1.05</v>
@@ -11464,7 +11526,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11472,7 +11534,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -11480,7 +11542,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11488,15 +11550,15 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B25">
         <v>1.05</v>
@@ -11504,7 +11566,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -11512,7 +11574,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -11520,7 +11582,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -11528,7 +11590,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B29">
         <v>2500</v>
@@ -11536,7 +11598,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -11544,7 +11606,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B31">
         <v>0.1</v>
@@ -11552,7 +11614,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -11560,7 +11622,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -11568,7 +11630,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11576,7 +11638,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B35">
         <v>50</v>
@@ -11584,7 +11646,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B36">
         <v>250</v>
@@ -11592,7 +11654,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B37">
         <v>2000</v>
@@ -11600,7 +11662,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -11608,47 +11670,47 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B44">
         <v>20000</v>
@@ -11656,7 +11718,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -11664,7 +11726,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -11672,7 +11734,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B47">
         <v>2500</v>
@@ -11680,7 +11742,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -11688,7 +11750,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B49">
         <v>100</v>
@@ -11696,7 +11758,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B50">
         <v>12</v>
@@ -11704,23 +11766,23 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -11728,7 +11790,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B54">
         <v>30</v>
@@ -11736,15 +11798,15 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B56">
         <v>28</v>
@@ -11752,7 +11814,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B57">
         <v>2000</v>
@@ -11760,7 +11822,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B58">
         <v>25000</v>
@@ -11768,31 +11830,31 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B62">
         <v>60</v>
@@ -11800,15 +11862,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B64">
         <v>30</v>
@@ -11816,23 +11878,23 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -11840,7 +11902,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B68">
         <v>24</v>
@@ -11848,7 +11910,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B69">
         <v>10</v>
@@ -11856,7 +11918,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -11864,7 +11926,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B71">
         <v>10</v>
@@ -11872,7 +11934,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -11880,7 +11942,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B73">
         <v>50</v>
@@ -11888,7 +11950,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -11896,7 +11958,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B75">
         <v>100</v>
@@ -11904,7 +11966,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B76">
         <v>1.09</v>
@@ -11912,7 +11974,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -11920,7 +11982,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B78">
         <v>50</v>
@@ -11928,7 +11990,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -11936,7 +11998,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -11944,7 +12006,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B81">
         <v>0.2</v>
@@ -11952,7 +12014,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -11960,7 +12022,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B83">
         <v>0.3</v>
@@ -11968,7 +12030,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B84">
         <v>1.5</v>
@@ -11976,7 +12038,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B85">
         <v>0.75</v>
@@ -11984,7 +12046,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B86">
         <v>0.4</v>
@@ -11992,7 +12054,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B87">
         <v>100</v>
@@ -12000,7 +12062,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B88">
         <v>600</v>
@@ -12008,7 +12070,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -12016,7 +12078,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -12024,7 +12086,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -12032,7 +12094,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -12040,7 +12102,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -12048,7 +12110,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -12056,7 +12118,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B95">
         <v>400</v>
@@ -12064,7 +12126,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B96">
         <v>0.3</v>
@@ -12072,7 +12134,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B97">
         <v>3</v>
@@ -12080,7 +12142,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B98">
         <v>0.5</v>
@@ -12088,7 +12150,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B99">
         <v>0.1</v>
@@ -12096,7 +12158,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B100">
         <v>0.3</v>
@@ -12104,7 +12166,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B101">
         <v>0.25</v>
@@ -12112,7 +12174,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B102">
         <v>500</v>
@@ -12120,7 +12182,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B103">
         <v>15</v>
@@ -12128,7 +12190,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B104">
         <v>150</v>
@@ -12136,7 +12198,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B105">
         <v>6</v>
@@ -12144,7 +12206,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -12152,7 +12214,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B107">
         <v>2500</v>
@@ -12160,7 +12222,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -12168,7 +12230,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B109">
         <v>30</v>
@@ -12176,7 +12238,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B110">
         <v>90</v>
@@ -12184,7 +12246,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B111">
         <v>0.5</v>
@@ -12192,7 +12254,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -12200,7 +12262,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -12208,10 +12270,10 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3076" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="665">
   <si>
     <t>id</t>
   </si>
@@ -1205,6 +1205,9 @@
   </si>
   <si>
     <t>active_power_per_level</t>
+  </si>
+  <si>
+    <t>active_duration_per_level</t>
   </si>
   <si>
     <t>DowsingRod</t>
@@ -7756,7 +7759,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7769,9 +7772,10 @@
     <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7802,10 +7806,13 @@
       <c r="J1" s="1" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -7814,13 +7821,13 @@
         <v>0.2</v>
       </c>
       <c r="D2">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>300</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2" t="s">
         <v>31</v>
@@ -7828,16 +7835,19 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
-        <v>31</v>
+      <c r="I2">
+        <v>5</v>
       </c>
       <c r="J2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7866,10 +7876,13 @@
       <c r="J3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -7898,10 +7911,13 @@
       <c r="J4">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -7930,10 +7946,13 @@
       <c r="J5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -7942,13 +7961,13 @@
         <v>0.25</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>31</v>
+      <c r="F6">
+        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
@@ -7962,10 +7981,13 @@
       <c r="J6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -7994,10 +8016,13 @@
       <c r="J7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -8026,10 +8051,13 @@
       <c r="J8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -8056,6 +8084,9 @@
         <v>31</v>
       </c>
       <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8089,16 +8120,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -8113,42 +8144,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -8192,16 +8223,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -8245,16 +8276,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -8298,16 +8329,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -8351,16 +8382,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -8396,7 +8427,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -8404,16 +8435,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -8457,16 +8488,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -8510,16 +8541,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8563,16 +8594,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8616,16 +8647,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8669,16 +8700,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8722,16 +8753,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8775,16 +8806,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8828,16 +8859,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B15" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8881,16 +8912,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8934,16 +8965,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -8987,16 +9018,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -9040,16 +9071,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -9093,16 +9124,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B20" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -9146,16 +9177,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -9199,16 +9230,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -9252,16 +9283,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -9305,16 +9336,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B24" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -9358,16 +9389,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B25" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -9411,16 +9442,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B26" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -9464,16 +9495,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -9517,16 +9548,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9570,16 +9601,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9615,7 +9646,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9623,16 +9654,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9668,7 +9699,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9676,16 +9707,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9721,7 +9752,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9729,16 +9760,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9774,7 +9805,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9782,16 +9813,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9827,7 +9858,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9860,13 +9891,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9884,27 +9915,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9936,16 +9967,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -9977,16 +10008,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -10018,16 +10049,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -10059,16 +10090,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -10129,51 +10160,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -10220,7 +10251,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -10288,27 +10319,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -10331,7 +10362,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -10354,7 +10385,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -10377,7 +10408,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -10400,7 +10431,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -10423,7 +10454,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -10446,7 +10477,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -10469,7 +10500,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -10492,7 +10523,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -10515,7 +10546,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -10559,48 +10590,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10621,10 +10652,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10641,7 +10672,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10662,10 +10693,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10682,7 +10713,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10703,10 +10734,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10723,7 +10754,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10744,10 +10775,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10764,7 +10795,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10785,10 +10816,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10805,7 +10836,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10826,10 +10857,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10846,7 +10877,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10867,10 +10898,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10887,7 +10918,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10908,10 +10939,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10928,7 +10959,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10949,10 +10980,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -10969,7 +11000,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -10990,10 +11021,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -11010,7 +11041,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11031,10 +11062,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -11051,7 +11082,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11072,10 +11103,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -11092,7 +11123,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11113,10 +11144,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -11133,7 +11164,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11154,10 +11185,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I15" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -11174,7 +11205,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11195,10 +11226,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I16" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -11235,19 +11266,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11366,15 +11397,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11382,7 +11413,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11390,7 +11421,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11398,7 +11429,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11406,15 +11437,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11422,7 +11453,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11430,7 +11461,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11438,7 +11469,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11446,7 +11477,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11454,15 +11485,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -11470,7 +11501,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -11478,7 +11509,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11486,7 +11517,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B16">
         <v>1.25</v>
@@ -11494,7 +11525,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -11502,15 +11533,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -11518,7 +11549,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B20">
         <v>1.05</v>
@@ -11526,7 +11557,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11534,7 +11565,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -11542,7 +11573,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11550,15 +11581,15 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B25">
         <v>1.05</v>
@@ -11566,7 +11597,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -11574,7 +11605,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -11582,7 +11613,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -11590,7 +11621,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B29">
         <v>2500</v>
@@ -11598,7 +11629,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -11606,7 +11637,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B31">
         <v>0.1</v>
@@ -11614,7 +11645,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -11622,7 +11653,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -11630,7 +11661,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11638,7 +11669,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B35">
         <v>50</v>
@@ -11646,7 +11677,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B36">
         <v>250</v>
@@ -11654,7 +11685,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B37">
         <v>2000</v>
@@ -11662,7 +11693,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -11670,47 +11701,47 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B44">
         <v>20000</v>
@@ -11718,7 +11749,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -11726,7 +11757,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -11734,7 +11765,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B47">
         <v>2500</v>
@@ -11742,7 +11773,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -11750,7 +11781,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B49">
         <v>100</v>
@@ -11758,7 +11789,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B50">
         <v>12</v>
@@ -11766,23 +11797,23 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -11790,7 +11821,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B54">
         <v>30</v>
@@ -11798,15 +11829,15 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B56">
         <v>28</v>
@@ -11814,7 +11845,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B57">
         <v>2000</v>
@@ -11822,7 +11853,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B58">
         <v>25000</v>
@@ -11830,31 +11861,31 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B62">
         <v>60</v>
@@ -11862,15 +11893,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B64">
         <v>30</v>
@@ -11878,23 +11909,23 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -11902,7 +11933,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B68">
         <v>24</v>
@@ -11910,7 +11941,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B69">
         <v>10</v>
@@ -11918,7 +11949,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -11926,7 +11957,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B71">
         <v>10</v>
@@ -11934,7 +11965,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -11942,7 +11973,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B73">
         <v>50</v>
@@ -11950,7 +11981,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -11958,7 +11989,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B75">
         <v>100</v>
@@ -11966,7 +11997,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B76">
         <v>1.09</v>
@@ -11974,7 +12005,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -11982,7 +12013,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B78">
         <v>50</v>
@@ -11990,7 +12021,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -11998,7 +12029,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -12006,7 +12037,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B81">
         <v>0.2</v>
@@ -12014,7 +12045,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -12022,7 +12053,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B83">
         <v>0.3</v>
@@ -12030,7 +12061,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B84">
         <v>1.5</v>
@@ -12038,7 +12069,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B85">
         <v>0.75</v>
@@ -12046,7 +12077,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B86">
         <v>0.4</v>
@@ -12054,7 +12085,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B87">
         <v>100</v>
@@ -12062,7 +12093,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B88">
         <v>600</v>
@@ -12070,7 +12101,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -12078,7 +12109,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -12086,7 +12117,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -12094,7 +12125,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -12102,7 +12133,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -12110,7 +12141,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -12118,7 +12149,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B95">
         <v>400</v>
@@ -12126,7 +12157,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B96">
         <v>0.3</v>
@@ -12134,7 +12165,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B97">
         <v>3</v>
@@ -12142,7 +12173,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B98">
         <v>0.5</v>
@@ -12150,7 +12181,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B99">
         <v>0.1</v>
@@ -12158,7 +12189,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B100">
         <v>0.3</v>
@@ -12166,7 +12197,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B101">
         <v>0.25</v>
@@ -12174,7 +12205,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B102">
         <v>500</v>
@@ -12182,7 +12213,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B103">
         <v>15</v>
@@ -12190,7 +12221,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B104">
         <v>150</v>
@@ -12198,7 +12229,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B105">
         <v>6</v>
@@ -12206,7 +12237,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -12214,7 +12245,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B107">
         <v>2500</v>
@@ -12222,7 +12253,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -12230,7 +12261,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B109">
         <v>30</v>
@@ -12238,7 +12269,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B110">
         <v>90</v>
@@ -12246,7 +12277,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B111">
         <v>0.5</v>
@@ -12254,7 +12285,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -12262,7 +12293,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -12270,10 +12301,10 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3095" uniqueCount="667">
   <si>
     <t>id</t>
   </si>
@@ -1208,6 +1208,12 @@
   </si>
   <si>
     <t>active_duration_per_level</t>
+  </si>
+  <si>
+    <t>active_charges</t>
+  </si>
+  <si>
+    <t>active_charges_per_level</t>
   </si>
   <si>
     <t>DowsingRod</t>
@@ -7759,7 +7765,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7773,9 +7779,11 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="27" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7809,10 +7817,16 @@
       <c r="K1" s="1" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -7844,10 +7858,16 @@
       <c r="K2">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -7879,10 +7899,16 @@
       <c r="K3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -7914,10 +7940,16 @@
       <c r="K4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -7949,10 +7981,16 @@
       <c r="K5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -7984,10 +8022,16 @@
       <c r="K6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -7996,7 +8040,7 @@
         <v>0.15</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -8010,8 +8054,8 @@
       <c r="H7" t="s">
         <v>31</v>
       </c>
-      <c r="I7" t="s">
-        <v>31</v>
+      <c r="I7">
+        <v>2</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
@@ -8019,10 +8063,16 @@
       <c r="K7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -8054,10 +8104,16 @@
       <c r="K8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -8087,6 +8143,12 @@
         <v>31</v>
       </c>
       <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8120,16 +8182,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -8144,42 +8206,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -8223,16 +8285,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B3" t="s">
         <v>416</v>
-      </c>
-      <c r="B3" t="s">
-        <v>414</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -8276,16 +8338,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -8329,16 +8391,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B5" t="s">
         <v>421</v>
-      </c>
-      <c r="B5" t="s">
-        <v>419</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -8382,16 +8444,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -8427,7 +8489,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -8435,16 +8497,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -8488,16 +8550,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -8541,16 +8603,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8594,16 +8656,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8647,16 +8709,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8700,16 +8762,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8753,16 +8815,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B13" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -8806,16 +8868,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -8859,16 +8921,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -8912,16 +8974,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B16" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -8965,16 +9027,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B17" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -9018,16 +9080,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B18" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -9071,16 +9133,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B19" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -9124,16 +9186,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B20" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -9177,16 +9239,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B21" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -9230,16 +9292,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B22" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -9283,16 +9345,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B23" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -9336,16 +9398,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B24" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -9389,16 +9451,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -9442,16 +9504,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B26" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -9495,16 +9557,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B27" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -9548,16 +9610,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9601,16 +9663,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B29" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9646,7 +9708,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9654,16 +9716,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B30" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9699,7 +9761,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9707,16 +9769,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9752,7 +9814,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9760,16 +9822,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B32" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -9805,7 +9867,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -9813,16 +9875,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B33" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -9858,7 +9920,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -9891,13 +9953,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -9915,27 +9977,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -9967,16 +10029,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -10008,16 +10070,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -10049,16 +10111,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C5" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -10090,16 +10152,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -10160,51 +10222,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -10251,7 +10313,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -10319,27 +10381,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -10362,7 +10424,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -10385,7 +10447,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -10408,7 +10470,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -10431,7 +10493,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -10454,7 +10516,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -10477,7 +10539,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -10500,7 +10562,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -10523,7 +10585,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B10">
         <v>9.99</v>
@@ -10546,7 +10608,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B11">
         <v>19.99</v>
@@ -10590,48 +10652,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10652,10 +10714,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10672,7 +10734,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10693,10 +10755,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10713,7 +10775,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10734,10 +10796,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10754,7 +10816,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10775,10 +10837,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -10795,7 +10857,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10816,10 +10878,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -10836,7 +10898,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10857,10 +10919,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -10877,7 +10939,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10898,10 +10960,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -10918,7 +10980,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -10939,10 +11001,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -10959,7 +11021,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -10980,10 +11042,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -11000,7 +11062,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -11021,10 +11083,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -11041,7 +11103,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11062,10 +11124,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I12" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -11082,7 +11144,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11103,10 +11165,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -11123,7 +11185,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11144,10 +11206,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -11164,7 +11226,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11185,10 +11247,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -11205,7 +11267,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11226,10 +11288,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I16" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -11266,19 +11328,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11397,15 +11459,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11413,7 +11475,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11421,7 +11483,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11429,7 +11491,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11437,15 +11499,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11453,7 +11515,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11461,7 +11523,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11469,7 +11531,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11477,7 +11539,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11485,15 +11547,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -11501,7 +11563,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -11509,7 +11571,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11517,7 +11579,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B16">
         <v>1.25</v>
@@ -11525,7 +11587,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -11533,15 +11595,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -11549,7 +11611,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B20">
         <v>1.05</v>
@@ -11557,7 +11619,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11565,7 +11627,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -11573,7 +11635,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11581,15 +11643,15 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B25">
         <v>1.05</v>
@@ -11597,7 +11659,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -11605,7 +11667,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -11613,7 +11675,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -11621,7 +11683,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B29">
         <v>2500</v>
@@ -11629,7 +11691,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -11637,7 +11699,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B31">
         <v>0.1</v>
@@ -11645,7 +11707,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -11653,7 +11715,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -11661,7 +11723,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11669,7 +11731,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B35">
         <v>50</v>
@@ -11677,7 +11739,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B36">
         <v>250</v>
@@ -11685,7 +11747,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B37">
         <v>2000</v>
@@ -11693,7 +11755,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -11701,47 +11763,47 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B44">
         <v>20000</v>
@@ -11749,7 +11811,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -11757,7 +11819,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -11765,7 +11827,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B47">
         <v>2500</v>
@@ -11773,7 +11835,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B48">
         <v>2</v>
@@ -11781,7 +11843,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B49">
         <v>100</v>
@@ -11789,7 +11851,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B50">
         <v>12</v>
@@ -11797,23 +11859,23 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -11821,7 +11883,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B54">
         <v>30</v>
@@ -11829,15 +11891,15 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B56">
         <v>28</v>
@@ -11845,7 +11907,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B57">
         <v>2000</v>
@@ -11853,7 +11915,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B58">
         <v>25000</v>
@@ -11861,31 +11923,31 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B62">
         <v>60</v>
@@ -11893,15 +11955,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B64">
         <v>30</v>
@@ -11909,23 +11971,23 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -11933,7 +11995,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B68">
         <v>24</v>
@@ -11941,7 +12003,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B69">
         <v>10</v>
@@ -11949,7 +12011,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -11957,7 +12019,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B71">
         <v>10</v>
@@ -11965,7 +12027,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -11973,7 +12035,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B73">
         <v>50</v>
@@ -11981,7 +12043,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -11989,7 +12051,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B75">
         <v>100</v>
@@ -11997,7 +12059,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B76">
         <v>1.09</v>
@@ -12005,7 +12067,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -12013,7 +12075,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B78">
         <v>50</v>
@@ -12021,7 +12083,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -12029,7 +12091,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B80">
         <v>0.2</v>
@@ -12037,7 +12099,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B81">
         <v>0.2</v>
@@ -12045,7 +12107,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -12053,7 +12115,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B83">
         <v>0.3</v>
@@ -12061,7 +12123,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B84">
         <v>1.5</v>
@@ -12069,7 +12131,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B85">
         <v>0.75</v>
@@ -12077,7 +12139,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B86">
         <v>0.4</v>
@@ -12085,7 +12147,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B87">
         <v>100</v>
@@ -12093,7 +12155,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B88">
         <v>600</v>
@@ -12101,7 +12163,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -12109,7 +12171,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -12117,7 +12179,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -12125,7 +12187,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -12133,7 +12195,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -12141,7 +12203,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -12149,7 +12211,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B95">
         <v>400</v>
@@ -12157,7 +12219,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B96">
         <v>0.3</v>
@@ -12165,7 +12227,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B97">
         <v>3</v>
@@ -12173,7 +12235,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B98">
         <v>0.5</v>
@@ -12181,7 +12243,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B99">
         <v>0.1</v>
@@ -12189,7 +12251,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B100">
         <v>0.3</v>
@@ -12197,7 +12259,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B101">
         <v>0.25</v>
@@ -12205,7 +12267,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B102">
         <v>500</v>
@@ -12213,7 +12275,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B103">
         <v>15</v>
@@ -12221,7 +12283,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B104">
         <v>150</v>
@@ -12229,7 +12291,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B105">
         <v>6</v>
@@ -12237,7 +12299,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -12245,7 +12307,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B107">
         <v>2500</v>
@@ -12253,7 +12315,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -12261,7 +12323,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B109">
         <v>30</v>
@@ -12269,7 +12331,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B110">
         <v>90</v>
@@ -12277,7 +12339,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B111">
         <v>0.5</v>
@@ -12285,7 +12347,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -12293,7 +12355,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -12301,10 +12363,10 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3095" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="713">
   <si>
     <t>id</t>
   </si>
@@ -1567,6 +1567,9 @@
     <t>RoyalChest</t>
   </si>
   <si>
+    <t>SeasonPass</t>
+  </si>
+  <si>
     <t>CardsSatchel</t>
   </si>
   <si>
@@ -1790,6 +1793,141 @@
   </si>
   <si>
     <t>daily.premium_xp_floor</t>
+  </si>
+  <si>
+    <t>pass.mission_xp</t>
+  </si>
+  <si>
+    <t>pass.level_xp_base</t>
+  </si>
+  <si>
+    <t>pass.level_xp_growth</t>
+  </si>
+  <si>
+    <t>pass.free_packs</t>
+  </si>
+  <si>
+    <t>Green,,Green,,Rose,,Green,,Green,Yellow,Green,,Green,,Rose,,Green,,Green,Yellow,Green,,Green,,Rose,,Green,,Green,Yellow,Green,,Green,,Rose,,Green,,Green,Rose</t>
+  </si>
+  <si>
+    <t>pass.free_gems</t>
+  </si>
+  <si>
+    <t>0,0,0,100,0,0,0,125,0,0,0,150,0,0,0,175,0,0,0,200,0,0,0,225,0,0,0,250,0,0,0,275,0,0,0,300,0,0,0,325</t>
+  </si>
+  <si>
+    <t>pass.free_gold_keys</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,1,0,0,0,0,0,0,0,0,0,1</t>
+  </si>
+  <si>
+    <t>pass.free_stardust</t>
+  </si>
+  <si>
+    <t>0,0,0,0,50,0,0,0,0,0,0,0,0,0,70,0,0,0,0,0,0,0,0,0,90,0,0,0,0,0,0,0,0,0,110,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>pass.paid_packs</t>
+  </si>
+  <si>
+    <t>Blue,Blue,Blue,Blue,Purple,Blue,Blue,Blue,Blue,Golden,Blue,Blue,Blue,Blue,Purple,Blue,Blue,Blue,Blue,Golden,Blue,Blue,Blue,Blue,Purple,Blue,Blue,Blue,Blue,Golden,Blue,Blue,Blue,Blue,Purple,Blue,Blue,Blue,Blue,Golden</t>
+  </si>
+  <si>
+    <t>pass.paid_gems</t>
+  </si>
+  <si>
+    <t>120,140,160,180,200,220,240,260,280,300,320,340,360,380,400,420,440,460,480,500,520,540,560,580,600,620,640,660,680,700,720,740,760,780,800,820,840,860,880,900</t>
+  </si>
+  <si>
+    <t>pass.paid_gold_keys</t>
+  </si>
+  <si>
+    <t>0,0,0,0,1,0,0,0,0,2,0,0,0,0,1,0,0,0,0,2,0,0,0,0,1,0,0,0,0,2,0,0,0,0,1,0,0,0,0,2</t>
+  </si>
+  <si>
+    <t>pass.paid_stardust</t>
+  </si>
+  <si>
+    <t>0,0,75,0,0,90,0,0,105,0,0,120,0,0,135,0,0,150,0,0,165,0,0,180,0,0,195,0,0,210,0,0,225,0,0,240,0,0,255,0</t>
+  </si>
+  <si>
+    <t>missions.board_size</t>
+  </si>
+  <si>
+    <t>missions.per_window</t>
+  </si>
+  <si>
+    <t>missions.window_hours</t>
+  </si>
+  <si>
+    <t>missions.weekly_quota</t>
+  </si>
+  <si>
+    <t>missions.gem_per_remaining</t>
+  </si>
+  <si>
+    <t>missions.gem_floor</t>
+  </si>
+  <si>
+    <t>missions.collect_minutes_min</t>
+  </si>
+  <si>
+    <t>missions.collect_minutes_max</t>
+  </si>
+  <si>
+    <t>missions.collect_floor</t>
+  </si>
+  <si>
+    <t>missions.population_band</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>missions.upgrade_band</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>missions.reveal_band</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>missions.build_band</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>missions.troops_band</t>
+  </si>
+  <si>
+    <t>3,10</t>
+  </si>
+  <si>
+    <t>missions.hero_level_band</t>
+  </si>
+  <si>
+    <t>missions.rooms_band</t>
+  </si>
+  <si>
+    <t>missions.depths_band</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>missions.packs_band</t>
+  </si>
+  <si>
+    <t>missions.reward_hours</t>
+  </si>
+  <si>
+    <t>missions.reward_gems</t>
   </si>
   <si>
     <t>research.tech_slots</t>
@@ -10366,7 +10504,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -10570,17 +10708,17 @@
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>2</v>
+      <c r="D9" t="s">
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10588,13 +10726,13 @@
         <v>513</v>
       </c>
       <c r="B10">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
         <v>378</v>
@@ -10603,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -10611,21 +10749,44 @@
         <v>514</v>
       </c>
       <c r="B11">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
         <v>378</v>
       </c>
       <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B12">
+        <v>19.99</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>
@@ -10652,48 +10813,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10734,7 +10895,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10775,7 +10936,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10816,7 +10977,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -10857,7 +11018,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -10898,7 +11059,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -10939,7 +11100,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10980,7 +11141,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -11021,7 +11182,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -11062,7 +11223,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -11103,7 +11264,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11144,7 +11305,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11185,7 +11346,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11226,7 +11387,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11267,7 +11428,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11328,19 +11489,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11451,7 +11612,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -11462,12 +11623,12 @@
         <v>483</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11475,7 +11636,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11483,7 +11644,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11491,7 +11652,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11499,15 +11660,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11515,7 +11676,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11523,7 +11684,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11531,7 +11692,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11539,7 +11700,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11547,15 +11708,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -11563,7 +11724,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -11571,7 +11732,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11579,7 +11740,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B16">
         <v>1.25</v>
@@ -11587,7 +11748,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -11595,15 +11756,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -11611,7 +11772,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B20">
         <v>1.05</v>
@@ -11619,7 +11780,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11627,7 +11788,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -11635,7 +11796,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11643,15 +11804,15 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B25">
         <v>1.05</v>
@@ -11659,7 +11820,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -11667,7 +11828,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -11675,7 +11836,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -11683,7 +11844,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B29">
         <v>2500</v>
@@ -11691,7 +11852,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -11699,7 +11860,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B31">
         <v>0.1</v>
@@ -11707,7 +11868,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -11715,7 +11876,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -11723,7 +11884,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11731,7 +11892,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B35">
         <v>50</v>
@@ -11739,7 +11900,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B36">
         <v>250</v>
@@ -11747,7 +11908,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B37">
         <v>2000</v>
@@ -11755,7 +11916,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -11763,47 +11924,47 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B44">
         <v>20000</v>
@@ -11811,551 +11972,551 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B47">
-        <v>2500</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>590</v>
-      </c>
-      <c r="B48">
-        <v>2</v>
+        <v>591</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>591</v>
-      </c>
-      <c r="B49">
-        <v>100</v>
+        <v>593</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>592</v>
-      </c>
-      <c r="B50">
-        <v>12</v>
+        <v>595</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>597</v>
-      </c>
-      <c r="B53">
-        <v>10</v>
+        <v>601</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>598</v>
-      </c>
-      <c r="B54">
-        <v>30</v>
+        <v>603</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B56">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B57">
-        <v>2000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B58">
-        <v>25000</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>604</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>605</v>
+        <v>610</v>
+      </c>
+      <c r="B59">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>606</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>608</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
+      </c>
+      <c r="B61">
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B62">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>611</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
+      </c>
+      <c r="B63">
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B64">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>618</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
+        <v>620</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>619</v>
-      </c>
-      <c r="B68">
-        <v>24</v>
+        <v>622</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>620</v>
-      </c>
-      <c r="B69">
-        <v>10</v>
+        <v>624</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>621</v>
-      </c>
-      <c r="B70">
-        <v>5</v>
+        <v>626</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>622</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
+        <v>627</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>623</v>
-      </c>
-      <c r="B72">
-        <v>2</v>
+        <v>628</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>624</v>
-      </c>
-      <c r="B73">
-        <v>50</v>
+        <v>630</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B75">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B76">
-        <v>1.09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B77">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B78">
-        <v>50</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B80">
-        <v>0.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B81">
-        <v>0.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>633</v>
-      </c>
-      <c r="B82">
-        <v>5</v>
+        <v>639</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>634</v>
-      </c>
-      <c r="B83">
-        <v>0.3</v>
+        <v>641</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B84">
-        <v>1.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B85">
-        <v>0.75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>637</v>
-      </c>
-      <c r="B86">
-        <v>0.4</v>
+        <v>645</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="B87">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="B88">
-        <v>600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>641</v>
-      </c>
-      <c r="B90">
-        <v>2</v>
+        <v>650</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>642</v>
-      </c>
-      <c r="B91">
-        <v>3</v>
+        <v>652</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>643</v>
-      </c>
-      <c r="B92">
-        <v>4</v>
+        <v>654</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>645</v>
-      </c>
-      <c r="B94">
-        <v>6</v>
+        <v>657</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="B95">
-        <v>400</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>647</v>
-      </c>
-      <c r="B96">
-        <v>0.3</v>
+        <v>660</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>648</v>
-      </c>
-      <c r="B97">
-        <v>3</v>
+        <v>662</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="B98">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="B99">
-        <v>0.1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="B100">
-        <v>0.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="B101">
-        <v>0.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="B102">
-        <v>500</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="B103">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="B104">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="B105">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="B107">
-        <v>2500</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="B109">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="B110">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="B111">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="B112">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -12363,10 +12524,258 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>665</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>666</v>
+        <v>680</v>
+      </c>
+      <c r="B114">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>681</v>
+      </c>
+      <c r="B115">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>682</v>
+      </c>
+      <c r="B116">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>683</v>
+      </c>
+      <c r="B117">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>684</v>
+      </c>
+      <c r="B118">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>685</v>
+      </c>
+      <c r="B119">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>686</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>687</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>688</v>
+      </c>
+      <c r="B122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>689</v>
+      </c>
+      <c r="B123">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>690</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>691</v>
+      </c>
+      <c r="B125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>692</v>
+      </c>
+      <c r="B126">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>693</v>
+      </c>
+      <c r="B127">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>694</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>695</v>
+      </c>
+      <c r="B129">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>696</v>
+      </c>
+      <c r="B130">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>697</v>
+      </c>
+      <c r="B131">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>698</v>
+      </c>
+      <c r="B132">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>699</v>
+      </c>
+      <c r="B133">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>700</v>
+      </c>
+      <c r="B134">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>701</v>
+      </c>
+      <c r="B135">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>702</v>
+      </c>
+      <c r="B136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>703</v>
+      </c>
+      <c r="B137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>704</v>
+      </c>
+      <c r="B138">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>705</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>706</v>
+      </c>
+      <c r="B140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>707</v>
+      </c>
+      <c r="B141">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>708</v>
+      </c>
+      <c r="B142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>709</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>710</v>
+      </c>
+      <c r="B144">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>711</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -1813,7 +1813,7 @@
     <t>pass.free_gems</t>
   </si>
   <si>
-    <t>0,0,0,100,0,0,0,125,0,0,0,150,0,0,0,175,0,0,0,200,0,0,0,225,0,0,0,250,0,0,0,275,0,0,0,300,0,0,0,325</t>
+    <t>0,100,0,100,0,125,0,125,0,0,0,150,0,175,0,175,0,200,0,200,0,225,0,225,0,250,0,250,0,0,0,275,0,300,0,300,0,325,0,325</t>
   </si>
   <si>
     <t>pass.free_gold_keys</t>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="717">
   <si>
     <t>id</t>
   </si>
@@ -1924,10 +1924,22 @@
     <t>missions.packs_band</t>
   </si>
   <si>
-    <t>missions.reward_hours</t>
+    <t>missions.hard_kinds</t>
+  </si>
+  <si>
+    <t>RaiseTownhall,BuildDistricts,LevelHeroes,ClearRooms,CompleteDepths</t>
+  </si>
+  <si>
+    <t>missions.hard_pack</t>
+  </si>
+  <si>
+    <t>missions.normal_pack</t>
   </si>
   <si>
     <t>missions.reward_gems</t>
+  </si>
+  <si>
+    <t>missions.reward_mana_fraction</t>
   </si>
   <si>
     <t>research.tech_slots</t>
@@ -11612,7 +11624,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B148"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -12206,96 +12218,96 @@
       <c r="A74" t="s">
         <v>631</v>
       </c>
-      <c r="B74">
-        <v>1.5</v>
+      <c r="B74" s="2" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>632</v>
-      </c>
-      <c r="B75">
-        <v>15</v>
+        <v>633</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>633</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
+        <v>634</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B78">
-        <v>2500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B80">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B81">
-        <v>12</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>639</v>
-      </c>
-      <c r="B82" s="2" t="s">
         <v>640</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>641</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>642</v>
+      <c r="B83">
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B84">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>643</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="B85">
-        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -12311,7 +12323,7 @@
         <v>647</v>
       </c>
       <c r="B87">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -12319,292 +12331,292 @@
         <v>648</v>
       </c>
       <c r="B88">
-        <v>2000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>649</v>
       </c>
-      <c r="B89">
-        <v>25000</v>
+      <c r="B89" s="2" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>650</v>
-      </c>
-      <c r="B90" s="2" t="s">
         <v>651</v>
+      </c>
+      <c r="B90">
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>652</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>653</v>
+      <c r="B91">
+        <v>2000</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>654</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
+      </c>
+      <c r="B92">
+        <v>25000</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>656</v>
-      </c>
-      <c r="B93">
-        <v>60</v>
+        <v>654</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>656</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>658</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="B95">
-        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>660</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>661</v>
+      <c r="B96">
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>661</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>664</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="B99">
-        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>666</v>
       </c>
-      <c r="B100">
-        <v>10</v>
+      <c r="B100" s="2" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B102">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B104">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B106">
-        <v>100</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B107">
-        <v>1.09</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B108">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B109">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B111">
-        <v>0.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B112">
-        <v>0.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B114">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B115">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B116">
-        <v>0.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B117">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B118">
-        <v>100</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B119">
-        <v>600</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B123">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -12612,170 +12624,194 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B125">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B126">
-        <v>400</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B127">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B129">
-        <v>0.5</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B130">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B131">
-        <v>0.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B132">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B133">
-        <v>500</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B134">
-        <v>15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B135">
-        <v>150</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B136">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B138">
-        <v>2500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B140">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B141">
-        <v>90</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B142">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>711</v>
-      </c>
-      <c r="B145" s="2" t="s">
         <v>712</v>
+      </c>
+      <c r="B145">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>713</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>714</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>715</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="715">
   <si>
     <t>id</t>
   </si>
@@ -1862,12 +1862,6 @@
   </si>
   <si>
     <t>missions.weekly_quota</t>
-  </si>
-  <si>
-    <t>missions.gem_per_remaining</t>
-  </si>
-  <si>
-    <t>missions.gem_floor</t>
   </si>
   <si>
     <t>missions.collect_minutes_min</t>
@@ -11624,7 +11618,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -12107,7 +12101,7 @@
         <v>611</v>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -12115,7 +12109,7 @@
         <v>612</v>
       </c>
       <c r="B61">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -12123,63 +12117,63 @@
         <v>613</v>
       </c>
       <c r="B62">
-        <v>12</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>614</v>
       </c>
-      <c r="B63">
-        <v>40</v>
+      <c r="B63" s="2" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>615</v>
-      </c>
-      <c r="B64">
-        <v>60</v>
+        <v>616</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -12187,12 +12181,12 @@
         <v>626</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>617</v>
@@ -12200,42 +12194,42 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>619</v>
+        <v>375</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>632</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>633</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>375</v>
+      <c r="B75">
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>634</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>374</v>
+      <c r="B76">
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -12243,7 +12237,7 @@
         <v>635</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -12251,7 +12245,7 @@
         <v>636</v>
       </c>
       <c r="B78">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -12259,7 +12253,7 @@
         <v>637</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -12267,7 +12261,7 @@
         <v>638</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -12275,7 +12269,7 @@
         <v>639</v>
       </c>
       <c r="B81">
-        <v>2500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -12283,63 +12277,63 @@
         <v>640</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>641</v>
       </c>
-      <c r="B83">
-        <v>100</v>
+      <c r="B83" s="2" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>642</v>
-      </c>
-      <c r="B84">
-        <v>12</v>
+        <v>643</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>643</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
+      </c>
+      <c r="B85">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>645</v>
-      </c>
-      <c r="B86" s="2" t="s">
         <v>646</v>
+      </c>
+      <c r="B86">
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>647</v>
       </c>
-      <c r="B87">
-        <v>10</v>
+      <c r="B87" s="2" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B88">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>649</v>
-      </c>
-      <c r="B89" s="2" t="s">
         <v>650</v>
+      </c>
+      <c r="B89">
+        <v>2000</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -12347,87 +12341,87 @@
         <v>651</v>
       </c>
       <c r="B90">
-        <v>28</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>652</v>
       </c>
-      <c r="B91">
-        <v>2000</v>
+      <c r="B91" s="2" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>653</v>
-      </c>
-      <c r="B92">
-        <v>25000</v>
+        <v>654</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>656</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
+      </c>
+      <c r="B94">
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B96">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>663</v>
-      </c>
-      <c r="B98">
-        <v>30</v>
+        <v>664</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>664</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
+      </c>
+      <c r="B99">
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>666</v>
-      </c>
-      <c r="B100" s="2" t="s">
         <v>667</v>
+      </c>
+      <c r="B100">
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -12435,7 +12429,7 @@
         <v>668</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -12443,7 +12437,7 @@
         <v>669</v>
       </c>
       <c r="B102">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -12459,7 +12453,7 @@
         <v>671</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -12467,7 +12461,7 @@
         <v>672</v>
       </c>
       <c r="B105">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -12483,7 +12477,7 @@
         <v>674</v>
       </c>
       <c r="B107">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -12491,7 +12485,7 @@
         <v>675</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -12499,7 +12493,7 @@
         <v>676</v>
       </c>
       <c r="B109">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -12507,7 +12501,7 @@
         <v>677</v>
       </c>
       <c r="B110">
-        <v>1.09</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -12515,7 +12509,7 @@
         <v>678</v>
       </c>
       <c r="B111">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -12523,7 +12517,7 @@
         <v>679</v>
       </c>
       <c r="B112">
-        <v>50</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -12531,7 +12525,7 @@
         <v>680</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -12539,7 +12533,7 @@
         <v>681</v>
       </c>
       <c r="B114">
-        <v>0.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -12547,7 +12541,7 @@
         <v>682</v>
       </c>
       <c r="B115">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -12555,7 +12549,7 @@
         <v>683</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -12563,7 +12557,7 @@
         <v>684</v>
       </c>
       <c r="B117">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -12571,7 +12565,7 @@
         <v>685</v>
       </c>
       <c r="B118">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -12579,7 +12573,7 @@
         <v>686</v>
       </c>
       <c r="B119">
-        <v>0.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -12587,7 +12581,7 @@
         <v>687</v>
       </c>
       <c r="B120">
-        <v>0.4</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -12595,7 +12589,7 @@
         <v>688</v>
       </c>
       <c r="B121">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -12603,7 +12597,7 @@
         <v>689</v>
       </c>
       <c r="B122">
-        <v>600</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -12619,7 +12613,7 @@
         <v>691</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -12627,7 +12621,7 @@
         <v>692</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -12635,7 +12629,7 @@
         <v>693</v>
       </c>
       <c r="B126">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -12643,7 +12637,7 @@
         <v>694</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -12651,7 +12645,7 @@
         <v>695</v>
       </c>
       <c r="B128">
-        <v>6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -12659,7 +12653,7 @@
         <v>696</v>
       </c>
       <c r="B129">
-        <v>400</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -12667,7 +12661,7 @@
         <v>697</v>
       </c>
       <c r="B130">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -12675,7 +12669,7 @@
         <v>698</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -12683,7 +12677,7 @@
         <v>699</v>
       </c>
       <c r="B132">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -12691,7 +12685,7 @@
         <v>700</v>
       </c>
       <c r="B133">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -12699,7 +12693,7 @@
         <v>701</v>
       </c>
       <c r="B134">
-        <v>0.3</v>
+        <v>500</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -12707,7 +12701,7 @@
         <v>702</v>
       </c>
       <c r="B135">
-        <v>0.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -12715,7 +12709,7 @@
         <v>703</v>
       </c>
       <c r="B136">
-        <v>500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -12723,7 +12717,7 @@
         <v>704</v>
       </c>
       <c r="B137">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -12731,7 +12725,7 @@
         <v>705</v>
       </c>
       <c r="B138">
-        <v>150</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -12739,7 +12733,7 @@
         <v>706</v>
       </c>
       <c r="B139">
-        <v>6</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -12747,7 +12741,7 @@
         <v>707</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -12755,7 +12749,7 @@
         <v>708</v>
       </c>
       <c r="B141">
-        <v>2500</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -12763,7 +12757,7 @@
         <v>709</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -12771,7 +12765,7 @@
         <v>710</v>
       </c>
       <c r="B143">
-        <v>30</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -12779,7 +12773,7 @@
         <v>711</v>
       </c>
       <c r="B144">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -12787,31 +12781,15 @@
         <v>712</v>
       </c>
       <c r="B145">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>713</v>
       </c>
-      <c r="B146">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B146" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="B147">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>715</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/balance/balance.xlsx
+++ b/balance/balance.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="661">
   <si>
     <t>id</t>
   </si>
@@ -550,9 +550,6 @@
     <t>workTime</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>goal_type</t>
   </si>
   <si>
@@ -595,9 +592,6 @@
     <t>First steps</t>
   </si>
   <si>
-    <t>Tap the dark ground to clear it. Find four stands of forest — you will want the timber.</t>
-  </si>
-  <si>
     <t>DiscoverFeature</t>
   </si>
   <si>
@@ -610,9 +604,6 @@
     <t>Forestry</t>
   </si>
   <si>
-    <t>Nothing here can be worked by hand yet. Research Forestry — it opens the woods and the berry bushes both.</t>
-  </si>
-  <si>
     <t>CompleteTech</t>
   </si>
   <si>
@@ -622,9 +613,6 @@
     <t>Timber!</t>
   </si>
   <si>
-    <t>Now tap the trees beside your Townhall. Twenty-five Wood buys a roof and a field.</t>
-  </si>
-  <si>
     <t>CollectResource</t>
   </si>
   <si>
@@ -634,27 +622,18 @@
     <t>A roof</t>
   </si>
   <si>
-    <t>Build a House. Somebody has to live here.</t>
-  </si>
-  <si>
     <t>BuildDistrict</t>
   </si>
   <si>
     <t>Rations</t>
   </si>
   <si>
-    <t>Tap the berry bush west of your Townhall for Food. Villagers eat.</t>
-  </si>
-  <si>
     <t>FirstVillager</t>
   </si>
   <si>
     <t>First villager</t>
   </si>
   <si>
-    <t>Train your first villager — your new House has room for two.</t>
-  </si>
-  <si>
     <t>ReachPopulation</t>
   </si>
   <si>
@@ -664,24 +643,15 @@
     <t>Tax day</t>
   </si>
   <si>
-    <t>Your villager pays rent. Tap the House to hurry it along — 30 Gold.</t>
-  </si>
-  <si>
     <t>Explorer</t>
   </si>
   <si>
-    <t>Push the fog back further. The land is worth knowing.</t>
-  </si>
-  <si>
     <t>DiscoverCells</t>
   </si>
   <si>
     <t>Fields</t>
   </si>
   <si>
-    <t>Research Agriculture: crop plots you can tap for Food.</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -691,51 +661,33 @@
     <t>First plot</t>
   </si>
   <si>
-    <t>Build two crop plots on open grass.</t>
-  </si>
-  <si>
     <t>ByHand</t>
   </si>
   <si>
     <t>By hand</t>
   </si>
   <si>
-    <t>Tap the plots for Food. Doing this forever is not the plan.</t>
-  </si>
-  <si>
     <t>Lumber</t>
   </si>
   <si>
-    <t>Chop enough Wood by hand to raise a Farm.</t>
-  </si>
-  <si>
     <t>HoldResource</t>
   </si>
   <si>
     <t>Tillage</t>
   </si>
   <si>
-    <t>Research Farming: a Farm that works the plots for you.</t>
-  </si>
-  <si>
     <t>Farming</t>
   </si>
   <si>
     <t>Farmhand</t>
   </si>
   <si>
-    <t>Build a Farm beside your plot.</t>
-  </si>
-  <si>
     <t>ToWork</t>
   </si>
   <si>
     <t>Put them to work</t>
   </si>
   <si>
-    <t>Assign a villager to the Farm. Now it harvests without you.</t>
-  </si>
-  <si>
     <t>AssignWorkers</t>
   </si>
   <si>
@@ -745,24 +697,15 @@
     <t>Growing town</t>
   </si>
   <si>
-    <t>Build a second House. The Wood is starting to add up.</t>
-  </si>
-  <si>
     <t>Neighbors</t>
   </si>
   <si>
-    <t>Train another villager — the new House has the room.</t>
-  </si>
-  <si>
     <t>SawTeeth</t>
   </si>
   <si>
     <t>Saw teeth</t>
   </si>
   <si>
-    <t>Research Saws. Hand-chopping has taken you as far as it goes.</t>
-  </si>
-  <si>
     <t>Saws</t>
   </si>
   <si>
@@ -772,51 +715,33 @@
     <t>The Sawmill</t>
   </si>
   <si>
-    <t>Build a Sawmill within reach of the forest.</t>
-  </si>
-  <si>
     <t>Crewed</t>
   </si>
   <si>
-    <t>Put three villagers to work — two of them on the Sawmill.</t>
-  </si>
-  <si>
     <t>ProperCapital</t>
   </si>
   <si>
     <t>A proper capital</t>
   </si>
   <si>
-    <t>Your Townhall is full. Upgrade it for room to build.</t>
-  </si>
-  <si>
     <t>UpgradeDistrict</t>
   </si>
   <si>
     <t>Levies</t>
   </si>
   <si>
-    <t>Research Taxes. A settled town pays its hall a little more.</t>
-  </si>
-  <si>
     <t>Taxes01</t>
   </si>
   <si>
     <t>Sawpits</t>
   </si>
   <si>
-    <t>Research Sawpits. Every swing at a tree brings back a little more.</t>
-  </si>
-  <si>
     <t>SawpitsI</t>
   </si>
   <si>
     <t>Regrowth</t>
   </si>
   <si>
-    <t>Research Reforesting. The stumps come back sooner.</t>
-  </si>
-  <si>
     <t>Reforesting01</t>
   </si>
   <si>
@@ -826,33 +751,21 @@
     <t>Further afield</t>
   </si>
   <si>
-    <t>The map is bigger than your fields. Keep clearing it.</t>
-  </si>
-  <si>
     <t>ArmedMen</t>
   </si>
   <si>
     <t>Armed men</t>
   </si>
   <si>
-    <t>There is a barrow west of your fields, and it is not empty. Research Warriors.</t>
-  </si>
-  <si>
     <t>Mustered</t>
   </si>
   <si>
-    <t>Build a Barracks. You will need Stone — there is rock to the east.</t>
-  </si>
-  <si>
     <t>FirstSoldier</t>
   </si>
   <si>
     <t>First soldier</t>
   </si>
   <si>
-    <t>Train your first soldier.</t>
-  </si>
-  <si>
     <t>TrainArmy</t>
   </si>
   <si>
@@ -862,9 +775,6 @@
     <t>A hero answers</t>
   </si>
   <si>
-    <t>Summon at the banner. The first call is free.</t>
-  </si>
-  <si>
     <t>OwnHeroes</t>
   </si>
   <si>
@@ -874,18 +784,12 @@
     <t>A company</t>
   </si>
   <si>
-    <t>Train twenty-four soldiers. One is a guard; a company is what takes a gate.</t>
-  </si>
-  <si>
     <t>DriveThemOut</t>
   </si>
   <si>
     <t>Drive them out</t>
   </si>
   <si>
-    <t>Orcs hold the mouth of the Hollow Barrow, and they are counting down. Clear the gate.</t>
-  </si>
-  <si>
     <t>ClearGarrisons</t>
   </si>
   <si>
@@ -895,9 +799,6 @@
     <t>Old stones</t>
   </si>
   <si>
-    <t>Claim the shrine east of the Townhall. It will hold your magic.</t>
-  </si>
-  <si>
     <t>ClaimLandmarks</t>
   </si>
   <si>
@@ -907,33 +808,21 @@
     <t>Attunement</t>
   </si>
   <si>
-    <t>Consecrate a Sanctum. The stones you claimed hum with something the city can hold.</t>
-  </si>
-  <si>
     <t>Consecration</t>
   </si>
   <si>
     <t>Mapmakers</t>
   </si>
   <si>
-    <t>Reveal 20 more cells — a map is drawn by walking it.</t>
-  </si>
-  <si>
     <t>Surveyors</t>
   </si>
   <si>
-    <t>Reveal 25 more — the far rings are dearer, and worth it.</t>
-  </si>
-  <si>
     <t>Highlands</t>
   </si>
   <si>
     <t>Into the highlands</t>
   </si>
   <si>
-    <t>Research Scaling Tools to climb the mountains.</t>
-  </si>
-  <si>
     <t>ScalingTools</t>
   </si>
   <si>
@@ -943,9 +832,6 @@
     <t>Put to sea</t>
   </si>
   <si>
-    <t>Research Sailing to cross open water.</t>
-  </si>
-  <si>
     <t>Sailing</t>
   </si>
   <si>
@@ -955,27 +841,18 @@
     <t>Into the dark</t>
   </si>
   <si>
-    <t>Send a party into the Hollow Barrow and survive one depth.</t>
-  </si>
-  <si>
     <t>ReachDepth</t>
   </si>
   <si>
     <t>Stoneworks</t>
   </si>
   <si>
-    <t>Build a Quarry. Tapping rock by hand has served its purpose.</t>
-  </si>
-  <si>
     <t>MoreRoom</t>
   </si>
   <si>
     <t>More room</t>
   </si>
   <si>
-    <t>Research Urban Planning to build Houses taller.</t>
-  </si>
-  <si>
     <t>UrbanPlanning</t>
   </si>
   <si>
@@ -985,36 +862,24 @@
     <t>Second story</t>
   </si>
   <si>
-    <t>Upgrade a House to level 2.</t>
-  </si>
-  <si>
     <t>FullHouse</t>
   </si>
   <si>
     <t>Full house</t>
   </si>
   <si>
-    <t>Grow to eight villagers.</t>
-  </si>
-  <si>
     <t>IronRoad</t>
   </si>
   <si>
     <t>The iron road</t>
   </si>
   <si>
-    <t>Iron lies in the northern ridge. Bring back ten.</t>
-  </si>
-  <si>
     <t>Architect</t>
   </si>
   <si>
     <t>The architect</t>
   </si>
   <si>
-    <t>Set the city's clerks to work. With them the Townhall may stand a level higher.</t>
-  </si>
-  <si>
     <t>Bureaucracy</t>
   </si>
   <si>
@@ -1024,9 +889,6 @@
     <t>Deep seams</t>
   </si>
   <si>
-    <t>The peaks give up ordinary stone. Research Mining and your quarrymen bring the iron out of them too.</t>
-  </si>
-  <si>
     <t>Mining</t>
   </si>
   <si>
@@ -1036,36 +898,24 @@
     <t>A grand capital</t>
   </si>
   <si>
-    <t>Raise the Townhall to level 3.</t>
-  </si>
-  <si>
     <t>TheSanctum</t>
   </si>
   <si>
     <t>A place for magic</t>
   </si>
   <si>
-    <t>Build the Sanctum.</t>
-  </si>
-  <si>
     <t>AWarband</t>
   </si>
   <si>
     <t>A warband</t>
   </si>
   <si>
-    <t>Sixty soldiers under arms. The deeper ruins are fought by companies.</t>
-  </si>
-  <si>
     <t>TheBarrowsPrize</t>
   </si>
   <si>
     <t>The Barrow’s Prize</t>
   </si>
   <si>
-    <t>Clear the Hollow Barrow to its floor.</t>
-  </si>
-  <si>
     <t>ClearRuins</t>
   </si>
   <si>
@@ -1075,34 +925,22 @@
     <t>Worn well</t>
   </si>
   <si>
-    <t>Attune an artifact to your kingdom.</t>
-  </si>
-  <si>
     <t>OwnArtifacts</t>
   </si>
   <si>
     <t>Leylines</t>
   </si>
   <si>
-    <t>Claim four of the old places.</t>
-  </si>
-  <si>
     <t>DeeperStill</t>
   </si>
   <si>
     <t>Deeper still</t>
   </si>
   <si>
-    <t>Reach depth five in any ruin.</t>
-  </si>
-  <si>
     <t>TheReliquary</t>
   </si>
   <si>
     <t>The Reliquary</t>
-  </si>
-  <si>
-    <t>Hold three artifacts at once.</t>
   </si>
   <si>
     <t>cards</t>
@@ -4800,23 +4638,22 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4859,2498 +4696,2336 @@
       <c r="N1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>186</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>187</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>188</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>189</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>190</v>
       </c>
-      <c r="F2">
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>55</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17">
+        <v>110</v>
+      </c>
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18">
+        <v>90</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19">
+        <v>110</v>
+      </c>
+      <c r="H19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20">
+        <v>140</v>
+      </c>
+      <c r="H20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21">
+        <v>140</v>
+      </c>
+      <c r="H21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>180</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22">
+        <v>150</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D24" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24">
+        <v>90</v>
+      </c>
+      <c r="H24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25">
+        <v>90</v>
+      </c>
+      <c r="H25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26">
+        <v>150</v>
+      </c>
+      <c r="H26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27">
+        <v>220</v>
+      </c>
+      <c r="H27" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28">
+        <v>350</v>
+      </c>
+      <c r="H28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>243</v>
+      </c>
+      <c r="B29" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" t="s">
+        <v>245</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29">
+        <v>350</v>
+      </c>
+      <c r="H29" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29" t="s">
+        <v>31</v>
+      </c>
+      <c r="N29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30">
+        <v>150</v>
+      </c>
+      <c r="H30" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30">
+        <v>20</v>
+      </c>
+      <c r="M30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" t="s">
+        <v>245</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31">
+        <v>400</v>
+      </c>
+      <c r="H31" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" t="s">
+        <v>31</v>
+      </c>
+      <c r="N31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" t="s">
+        <v>252</v>
+      </c>
+      <c r="C32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32">
+        <v>250</v>
+      </c>
+      <c r="H32" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32" t="s">
+        <v>31</v>
+      </c>
+      <c r="N32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" t="s">
+        <v>256</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33">
+        <v>170</v>
+      </c>
+      <c r="H33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" t="s">
+        <v>31</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" t="s">
+        <v>258</v>
+      </c>
+      <c r="C34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>450</v>
+      </c>
+      <c r="H34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" t="s">
+        <v>260</v>
+      </c>
+      <c r="C35" t="s">
+        <v>205</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35">
+        <v>200</v>
+      </c>
+      <c r="H35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36">
+        <v>250</v>
+      </c>
+      <c r="H36" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>262</v>
+      </c>
+      <c r="B37" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37">
+        <v>220</v>
+      </c>
+      <c r="H37" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" t="s">
+        <v>31</v>
+      </c>
+      <c r="M37" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>265</v>
+      </c>
+      <c r="B38" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38">
+        <v>270</v>
+      </c>
+      <c r="H38" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M38" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>268</v>
+      </c>
+      <c r="B39" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39">
+        <v>200</v>
+      </c>
+      <c r="H39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39">
+        <v>150</v>
+      </c>
+      <c r="L39">
+        <v>25</v>
+      </c>
+      <c r="M39">
+        <v>2</v>
+      </c>
+      <c r="N39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" t="s">
+        <v>271</v>
+      </c>
+      <c r="C40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40">
+        <v>290</v>
+      </c>
+      <c r="H40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40">
+        <v>2</v>
+      </c>
+      <c r="N40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" t="s">
+        <v>273</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>274</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41">
+        <v>240</v>
+      </c>
+      <c r="H41" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B42" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" t="s">
+        <v>231</v>
+      </c>
+      <c r="D42" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>280</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>277</v>
+      </c>
+      <c r="B43" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43">
+        <v>310</v>
+      </c>
+      <c r="H43" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43">
+        <v>40</v>
+      </c>
+      <c r="J43" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" t="s">
+        <v>280</v>
+      </c>
+      <c r="C44" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44">
+        <v>30</v>
+      </c>
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44">
+        <v>380</v>
+      </c>
+      <c r="H44" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" t="s">
+        <v>31</v>
+      </c>
+      <c r="M44" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" t="s">
+        <v>283</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45">
+        <v>450</v>
+      </c>
+      <c r="H45" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>284</v>
+      </c>
+      <c r="B46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" t="s">
+        <v>286</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46">
+        <v>380</v>
+      </c>
+      <c r="H46" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" t="s">
+        <v>31</v>
+      </c>
+      <c r="N46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>287</v>
+      </c>
+      <c r="B47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C47" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="G47">
+        <v>600</v>
+      </c>
+      <c r="H47" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47">
+        <v>250</v>
+      </c>
+      <c r="L47" t="s">
+        <v>31</v>
+      </c>
+      <c r="M47" t="s">
+        <v>31</v>
+      </c>
+      <c r="N47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>289</v>
+      </c>
+      <c r="B48" t="s">
+        <v>290</v>
+      </c>
+      <c r="C48" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48">
+        <v>530</v>
+      </c>
+      <c r="H48" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48">
+        <v>40</v>
+      </c>
+      <c r="K48" t="s">
+        <v>31</v>
+      </c>
+      <c r="L48" t="s">
+        <v>31</v>
+      </c>
+      <c r="M48" t="s">
+        <v>31</v>
+      </c>
+      <c r="N48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" t="s">
+        <v>292</v>
+      </c>
+      <c r="C49" t="s">
+        <v>245</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49">
+        <v>450</v>
+      </c>
+      <c r="H49" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49">
+        <v>60</v>
+      </c>
+      <c r="J49" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" t="s">
+        <v>31</v>
+      </c>
+      <c r="L49" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" t="s">
+        <v>31</v>
+      </c>
+      <c r="N49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>293</v>
+      </c>
+      <c r="B50" t="s">
+        <v>294</v>
+      </c>
+      <c r="C50" t="s">
+        <v>295</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50">
+        <v>400</v>
+      </c>
+      <c r="H50" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" t="s">
+        <v>31</v>
+      </c>
+      <c r="L50">
+        <v>20</v>
+      </c>
+      <c r="M50" t="s">
+        <v>31</v>
+      </c>
+      <c r="N50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>296</v>
+      </c>
+      <c r="B51" t="s">
+        <v>297</v>
+      </c>
+      <c r="C51" t="s">
+        <v>298</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51">
+        <v>350</v>
+      </c>
+      <c r="H51" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51">
+        <v>18</v>
+      </c>
+      <c r="M51" t="s">
+        <v>31</v>
+      </c>
+      <c r="N51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>299</v>
+      </c>
+      <c r="B52" t="s">
+        <v>299</v>
+      </c>
+      <c r="C52" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4">
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52">
+        <v>750</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52">
+        <v>60</v>
+      </c>
+      <c r="K52" t="s">
+        <v>31</v>
+      </c>
+      <c r="L52" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" t="s">
+        <v>31</v>
+      </c>
+      <c r="N52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>300</v>
+      </c>
+      <c r="B53" t="s">
+        <v>301</v>
+      </c>
+      <c r="C53" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53">
+        <v>600</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53">
+        <v>90</v>
+      </c>
+      <c r="K53" t="s">
+        <v>31</v>
+      </c>
+      <c r="L53">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="M53" t="s">
+        <v>31</v>
+      </c>
+      <c r="N53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>302</v>
+      </c>
+      <c r="B54" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" t="s">
+        <v>298</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54">
+        <v>900</v>
+      </c>
+      <c r="H54" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54">
         <v>200</v>
       </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5">
-        <v>40</v>
-      </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>55</v>
-      </c>
-      <c r="I7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9">
-        <v>80</v>
-      </c>
-      <c r="I9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
-      <c r="O9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" t="s">
-        <v>194</v>
-      </c>
-      <c r="E10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10">
-        <v>60</v>
-      </c>
-      <c r="I10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10">
-        <v>6</v>
-      </c>
-      <c r="O10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11">
-        <v>55</v>
-      </c>
-      <c r="I11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>221</v>
-      </c>
-      <c r="B12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" t="s">
-        <v>223</v>
-      </c>
-      <c r="D12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12">
-        <v>20</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" t="s">
-        <v>225</v>
-      </c>
-      <c r="D13" t="s">
-        <v>226</v>
-      </c>
-      <c r="E13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13">
-        <v>40</v>
-      </c>
-      <c r="I13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" t="s">
-        <v>31</v>
-      </c>
-      <c r="O13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" t="s">
-        <v>194</v>
-      </c>
-      <c r="E14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>230</v>
-      </c>
-      <c r="B15" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" t="s">
-        <v>231</v>
-      </c>
-      <c r="D15" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15">
-        <v>85</v>
-      </c>
-      <c r="I15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" t="s">
-        <v>31</v>
-      </c>
-      <c r="M15" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" t="s">
-        <v>233</v>
-      </c>
-      <c r="C16" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16">
-        <v>85</v>
-      </c>
-      <c r="I16" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" t="s">
-        <v>31</v>
-      </c>
-      <c r="O16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" t="s">
-        <v>202</v>
-      </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17">
-        <v>110</v>
-      </c>
-      <c r="I17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" t="s">
-        <v>31</v>
-      </c>
-      <c r="O17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" t="s">
-        <v>239</v>
-      </c>
-      <c r="C18" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18">
-        <v>90</v>
-      </c>
-      <c r="I18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" t="s">
-        <v>31</v>
-      </c>
-      <c r="O18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" t="s">
-        <v>244</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19">
-        <v>110</v>
-      </c>
-      <c r="I19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" t="s">
-        <v>31</v>
-      </c>
-      <c r="M19" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" t="s">
-        <v>31</v>
-      </c>
-      <c r="O19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" t="s">
-        <v>246</v>
-      </c>
-      <c r="C20" t="s">
-        <v>247</v>
-      </c>
-      <c r="D20" t="s">
-        <v>202</v>
-      </c>
-      <c r="E20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20">
-        <v>140</v>
-      </c>
-      <c r="I20" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" t="s">
-        <v>31</v>
-      </c>
-      <c r="L20" t="s">
-        <v>31</v>
-      </c>
-      <c r="M20" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20">
-        <v>2</v>
-      </c>
-      <c r="O20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" t="s">
-        <v>248</v>
-      </c>
-      <c r="C21" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21">
-        <v>140</v>
-      </c>
-      <c r="I21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" t="s">
-        <v>31</v>
-      </c>
-      <c r="M21" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21">
-        <v>2</v>
-      </c>
-      <c r="O21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>250</v>
-      </c>
-      <c r="B22" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" t="s">
-        <v>252</v>
-      </c>
-      <c r="D22" t="s">
-        <v>253</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22">
-        <v>180</v>
-      </c>
-      <c r="I22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" t="s">
-        <v>31</v>
-      </c>
-      <c r="L22">
-        <v>150</v>
-      </c>
-      <c r="M22" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>254</v>
-      </c>
-      <c r="B23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" t="s">
-        <v>255</v>
-      </c>
-      <c r="D23" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23">
-        <v>80</v>
-      </c>
-      <c r="I23" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" t="s">
-        <v>31</v>
-      </c>
-      <c r="L23" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23">
-        <v>2</v>
-      </c>
-      <c r="O23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>257</v>
-      </c>
-      <c r="B24" t="s">
-        <v>257</v>
-      </c>
-      <c r="C24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E24" t="s">
-        <v>259</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24">
-        <v>90</v>
-      </c>
-      <c r="I24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" t="s">
-        <v>31</v>
-      </c>
-      <c r="M24" t="s">
-        <v>31</v>
-      </c>
-      <c r="N24" t="s">
-        <v>31</v>
-      </c>
-      <c r="O24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" t="s">
-        <v>260</v>
-      </c>
-      <c r="C25" t="s">
-        <v>261</v>
-      </c>
-      <c r="D25" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" t="s">
-        <v>262</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25">
-        <v>90</v>
-      </c>
-      <c r="I25" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" t="s">
-        <v>31</v>
-      </c>
-      <c r="M25" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" t="s">
-        <v>31</v>
-      </c>
-      <c r="O25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" t="s">
-        <v>265</v>
-      </c>
-      <c r="D26" t="s">
-        <v>214</v>
-      </c>
-      <c r="E26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26">
-        <v>150</v>
-      </c>
-      <c r="I26" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" t="s">
-        <v>31</v>
-      </c>
-      <c r="M26" t="s">
-        <v>31</v>
-      </c>
-      <c r="N26">
-        <v>2</v>
-      </c>
-      <c r="O26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>266</v>
-      </c>
-      <c r="B27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C27" t="s">
-        <v>268</v>
-      </c>
-      <c r="D27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27">
-        <v>220</v>
-      </c>
-      <c r="I27" t="s">
-        <v>31</v>
-      </c>
-      <c r="J27" t="s">
-        <v>31</v>
-      </c>
-      <c r="K27" t="s">
-        <v>31</v>
-      </c>
-      <c r="L27" t="s">
-        <v>31</v>
-      </c>
-      <c r="M27" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>269</v>
-      </c>
-      <c r="B28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C28" t="s">
-        <v>270</v>
-      </c>
-      <c r="D28" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28">
-        <v>350</v>
-      </c>
-      <c r="I28" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" t="s">
-        <v>31</v>
-      </c>
-      <c r="L28" t="s">
-        <v>31</v>
-      </c>
-      <c r="M28" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" t="s">
-        <v>31</v>
-      </c>
-      <c r="O28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B29" t="s">
-        <v>272</v>
-      </c>
-      <c r="C29" t="s">
-        <v>273</v>
-      </c>
-      <c r="D29" t="s">
-        <v>274</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29">
-        <v>350</v>
-      </c>
-      <c r="I29" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" t="s">
-        <v>31</v>
-      </c>
-      <c r="K29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L29" t="s">
-        <v>31</v>
-      </c>
-      <c r="M29" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B30" t="s">
-        <v>276</v>
-      </c>
-      <c r="C30" t="s">
-        <v>277</v>
-      </c>
-      <c r="D30" t="s">
-        <v>278</v>
-      </c>
-      <c r="E30" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
-      </c>
-      <c r="G30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30">
-        <v>150</v>
-      </c>
-      <c r="I30" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" t="s">
-        <v>31</v>
-      </c>
-      <c r="K30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" t="s">
-        <v>31</v>
-      </c>
-      <c r="M30">
-        <v>20</v>
-      </c>
-      <c r="N30" t="s">
-        <v>31</v>
-      </c>
-      <c r="O30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>279</v>
-      </c>
-      <c r="B31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C31" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" t="s">
-        <v>274</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31">
-        <v>24</v>
-      </c>
-      <c r="G31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31">
-        <v>400</v>
-      </c>
-      <c r="I31" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K31" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M31" t="s">
-        <v>31</v>
-      </c>
-      <c r="N31" t="s">
-        <v>31</v>
-      </c>
-      <c r="O31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>282</v>
-      </c>
-      <c r="B32" t="s">
-        <v>283</v>
-      </c>
-      <c r="C32" t="s">
-        <v>284</v>
-      </c>
-      <c r="D32" t="s">
-        <v>285</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32">
-        <v>250</v>
-      </c>
-      <c r="I32" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M32" t="s">
-        <v>31</v>
-      </c>
-      <c r="N32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>286</v>
-      </c>
-      <c r="B33" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" t="s">
-        <v>289</v>
-      </c>
-      <c r="E33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33">
-        <v>170</v>
-      </c>
-      <c r="I33" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" t="s">
-        <v>31</v>
-      </c>
-      <c r="M33" t="s">
-        <v>31</v>
-      </c>
-      <c r="N33">
-        <v>3</v>
-      </c>
-      <c r="O33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>290</v>
-      </c>
-      <c r="B34" t="s">
-        <v>291</v>
-      </c>
-      <c r="C34" t="s">
-        <v>292</v>
-      </c>
-      <c r="D34" t="s">
-        <v>194</v>
-      </c>
-      <c r="E34" t="s">
-        <v>293</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34">
-        <v>450</v>
-      </c>
-      <c r="I34" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" t="s">
-        <v>31</v>
-      </c>
-      <c r="L34" t="s">
-        <v>31</v>
-      </c>
-      <c r="M34" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>294</v>
-      </c>
-      <c r="B35" t="s">
-        <v>294</v>
-      </c>
-      <c r="C35" t="s">
-        <v>295</v>
-      </c>
-      <c r="D35" t="s">
-        <v>214</v>
-      </c>
-      <c r="E35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35">
-        <v>20</v>
-      </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35">
-        <v>200</v>
-      </c>
-      <c r="I35" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" t="s">
-        <v>31</v>
-      </c>
-      <c r="M35" t="s">
-        <v>31</v>
-      </c>
-      <c r="N35" t="s">
-        <v>31</v>
-      </c>
-      <c r="O35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>296</v>
-      </c>
-      <c r="B36" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" t="s">
-        <v>297</v>
-      </c>
-      <c r="D36" t="s">
-        <v>214</v>
-      </c>
-      <c r="E36" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36">
-        <v>25</v>
-      </c>
-      <c r="G36" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36">
-        <v>250</v>
-      </c>
-      <c r="I36" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" t="s">
-        <v>31</v>
-      </c>
-      <c r="K36" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" t="s">
-        <v>31</v>
-      </c>
-      <c r="M36" t="s">
-        <v>31</v>
-      </c>
-      <c r="N36" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>298</v>
-      </c>
-      <c r="B37" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" t="s">
-        <v>300</v>
-      </c>
-      <c r="D37" t="s">
-        <v>194</v>
-      </c>
-      <c r="E37" t="s">
-        <v>301</v>
-      </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37">
-        <v>220</v>
-      </c>
-      <c r="I37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" t="s">
-        <v>31</v>
-      </c>
-      <c r="K37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L37" t="s">
-        <v>31</v>
-      </c>
-      <c r="M37" t="s">
-        <v>31</v>
-      </c>
-      <c r="N37" t="s">
-        <v>31</v>
-      </c>
-      <c r="O37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>302</v>
-      </c>
-      <c r="B38" t="s">
-        <v>303</v>
-      </c>
-      <c r="C38" t="s">
-        <v>304</v>
-      </c>
-      <c r="D38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" t="s">
-        <v>305</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38">
-        <v>270</v>
-      </c>
-      <c r="I38" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" t="s">
-        <v>31</v>
-      </c>
-      <c r="K38" t="s">
-        <v>31</v>
-      </c>
-      <c r="L38" t="s">
-        <v>31</v>
-      </c>
-      <c r="M38" t="s">
-        <v>31</v>
-      </c>
-      <c r="N38" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>306</v>
-      </c>
-      <c r="B39" t="s">
-        <v>307</v>
-      </c>
-      <c r="C39" t="s">
-        <v>308</v>
-      </c>
-      <c r="D39" t="s">
-        <v>309</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H39">
-        <v>200</v>
-      </c>
-      <c r="I39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" t="s">
-        <v>31</v>
-      </c>
-      <c r="K39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L39">
-        <v>150</v>
-      </c>
-      <c r="M39">
-        <v>25</v>
-      </c>
-      <c r="N39">
-        <v>2</v>
-      </c>
-      <c r="O39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>310</v>
-      </c>
-      <c r="B40" t="s">
-        <v>310</v>
-      </c>
-      <c r="C40" t="s">
-        <v>311</v>
-      </c>
-      <c r="D40" t="s">
-        <v>202</v>
-      </c>
-      <c r="E40" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40">
-        <v>290</v>
-      </c>
-      <c r="I40" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K40" t="s">
-        <v>31</v>
-      </c>
-      <c r="L40" t="s">
-        <v>31</v>
-      </c>
-      <c r="M40" t="s">
-        <v>31</v>
-      </c>
-      <c r="N40">
-        <v>2</v>
-      </c>
-      <c r="O40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>312</v>
-      </c>
-      <c r="B41" t="s">
-        <v>313</v>
-      </c>
-      <c r="C41" t="s">
-        <v>314</v>
-      </c>
-      <c r="D41" t="s">
-        <v>194</v>
-      </c>
-      <c r="E41" t="s">
-        <v>315</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41">
-        <v>240</v>
-      </c>
-      <c r="I41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" t="s">
-        <v>31</v>
-      </c>
-      <c r="K41" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" t="s">
-        <v>31</v>
-      </c>
-      <c r="O41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B42" t="s">
-        <v>317</v>
-      </c>
-      <c r="C42" t="s">
-        <v>318</v>
-      </c>
-      <c r="D42" t="s">
-        <v>253</v>
-      </c>
-      <c r="E42" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>2</v>
-      </c>
-      <c r="H42">
-        <v>280</v>
-      </c>
-      <c r="I42" t="s">
-        <v>31</v>
-      </c>
-      <c r="J42" t="s">
-        <v>31</v>
-      </c>
-      <c r="K42">
-        <v>20</v>
-      </c>
-      <c r="L42" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" t="s">
-        <v>31</v>
-      </c>
-      <c r="N42" t="s">
-        <v>31</v>
-      </c>
-      <c r="O42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>319</v>
-      </c>
-      <c r="B43" t="s">
-        <v>320</v>
-      </c>
-      <c r="C43" t="s">
-        <v>321</v>
-      </c>
-      <c r="D43" t="s">
-        <v>208</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="G43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43">
-        <v>310</v>
-      </c>
-      <c r="I43" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43">
-        <v>40</v>
-      </c>
-      <c r="K43" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" t="s">
-        <v>31</v>
-      </c>
-      <c r="M43" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>322</v>
-      </c>
-      <c r="B44" t="s">
-        <v>323</v>
-      </c>
-      <c r="C44" t="s">
-        <v>324</v>
-      </c>
-      <c r="D44" t="s">
-        <v>198</v>
-      </c>
-      <c r="E44" t="s">
-        <v>134</v>
-      </c>
-      <c r="F44">
-        <v>30</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44">
-        <v>380</v>
-      </c>
-      <c r="I44" t="s">
-        <v>31</v>
-      </c>
-      <c r="J44" t="s">
-        <v>31</v>
-      </c>
-      <c r="K44" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" t="s">
-        <v>31</v>
-      </c>
-      <c r="M44" t="s">
-        <v>31</v>
-      </c>
-      <c r="N44" t="s">
-        <v>31</v>
-      </c>
-      <c r="O44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>325</v>
-      </c>
-      <c r="B45" t="s">
-        <v>326</v>
-      </c>
-      <c r="C45" t="s">
-        <v>327</v>
-      </c>
-      <c r="D45" t="s">
-        <v>194</v>
-      </c>
-      <c r="E45" t="s">
-        <v>328</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45">
-        <v>450</v>
-      </c>
-      <c r="I45" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" t="s">
-        <v>31</v>
-      </c>
-      <c r="K45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L45" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" t="s">
-        <v>31</v>
-      </c>
-      <c r="N45" t="s">
-        <v>31</v>
-      </c>
-      <c r="O45" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>329</v>
-      </c>
-      <c r="B46" t="s">
-        <v>330</v>
-      </c>
-      <c r="C46" t="s">
-        <v>331</v>
-      </c>
-      <c r="D46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E46" t="s">
-        <v>332</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46">
-        <v>380</v>
-      </c>
-      <c r="I46" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" t="s">
-        <v>31</v>
-      </c>
-      <c r="K46" t="s">
-        <v>31</v>
-      </c>
-      <c r="L46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M46" t="s">
-        <v>31</v>
-      </c>
-      <c r="N46" t="s">
-        <v>31</v>
-      </c>
-      <c r="O46" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>333</v>
-      </c>
-      <c r="B47" t="s">
-        <v>334</v>
-      </c>
-      <c r="C47" t="s">
-        <v>335</v>
-      </c>
-      <c r="D47" t="s">
-        <v>253</v>
-      </c>
-      <c r="E47" t="s">
-        <v>30</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>3</v>
-      </c>
-      <c r="H47">
-        <v>600</v>
-      </c>
-      <c r="I47" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" t="s">
-        <v>31</v>
-      </c>
-      <c r="K47" t="s">
-        <v>31</v>
-      </c>
-      <c r="L47">
-        <v>250</v>
-      </c>
-      <c r="M47" t="s">
-        <v>31</v>
-      </c>
-      <c r="N47" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>336</v>
-      </c>
-      <c r="B48" t="s">
-        <v>337</v>
-      </c>
-      <c r="C48" t="s">
-        <v>338</v>
-      </c>
-      <c r="D48" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" t="s">
-        <v>58</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48">
-        <v>530</v>
-      </c>
-      <c r="I48" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" t="s">
-        <v>31</v>
-      </c>
-      <c r="K48">
-        <v>40</v>
-      </c>
-      <c r="L48" t="s">
-        <v>31</v>
-      </c>
-      <c r="M48" t="s">
-        <v>31</v>
-      </c>
-      <c r="N48" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>339</v>
-      </c>
-      <c r="B49" t="s">
-        <v>340</v>
-      </c>
-      <c r="C49" t="s">
-        <v>341</v>
-      </c>
-      <c r="D49" t="s">
-        <v>274</v>
-      </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49">
-        <v>60</v>
-      </c>
-      <c r="G49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49">
-        <v>450</v>
-      </c>
-      <c r="I49" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49">
-        <v>60</v>
-      </c>
-      <c r="K49" t="s">
-        <v>31</v>
-      </c>
-      <c r="L49" t="s">
-        <v>31</v>
-      </c>
-      <c r="M49" t="s">
-        <v>31</v>
-      </c>
-      <c r="N49" t="s">
-        <v>31</v>
-      </c>
-      <c r="O49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>342</v>
-      </c>
-      <c r="B50" t="s">
-        <v>343</v>
-      </c>
-      <c r="C50" t="s">
-        <v>344</v>
-      </c>
-      <c r="D50" t="s">
-        <v>345</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>31</v>
-      </c>
-      <c r="H50">
-        <v>400</v>
-      </c>
-      <c r="I50" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" t="s">
-        <v>31</v>
-      </c>
-      <c r="K50" t="s">
-        <v>31</v>
-      </c>
-      <c r="L50" t="s">
-        <v>31</v>
-      </c>
-      <c r="M50">
-        <v>20</v>
-      </c>
-      <c r="N50" t="s">
-        <v>31</v>
-      </c>
-      <c r="O50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>346</v>
-      </c>
-      <c r="B51" t="s">
-        <v>347</v>
-      </c>
-      <c r="C51" t="s">
-        <v>348</v>
-      </c>
-      <c r="D51" t="s">
-        <v>349</v>
-      </c>
-      <c r="E51" t="s">
-        <v>31</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>31</v>
-      </c>
-      <c r="H51">
-        <v>350</v>
-      </c>
-      <c r="I51" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" t="s">
-        <v>31</v>
-      </c>
-      <c r="K51" t="s">
-        <v>31</v>
-      </c>
-      <c r="L51" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51">
-        <v>18</v>
-      </c>
-      <c r="N51" t="s">
-        <v>31</v>
-      </c>
-      <c r="O51" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>350</v>
-      </c>
-      <c r="B52" t="s">
-        <v>350</v>
-      </c>
-      <c r="C52" t="s">
-        <v>351</v>
-      </c>
-      <c r="D52" t="s">
-        <v>289</v>
-      </c>
-      <c r="E52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52">
-        <v>4</v>
-      </c>
-      <c r="G52" t="s">
-        <v>31</v>
-      </c>
-      <c r="H52">
-        <v>750</v>
-      </c>
-      <c r="I52" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" t="s">
-        <v>31</v>
-      </c>
-      <c r="K52">
-        <v>60</v>
-      </c>
-      <c r="L52" t="s">
-        <v>31</v>
-      </c>
-      <c r="M52" t="s">
-        <v>31</v>
-      </c>
-      <c r="N52" t="s">
-        <v>31</v>
-      </c>
-      <c r="O52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>352</v>
-      </c>
-      <c r="B53" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" t="s">
-        <v>354</v>
-      </c>
-      <c r="D53" t="s">
-        <v>309</v>
-      </c>
-      <c r="E53" t="s">
-        <v>31</v>
-      </c>
-      <c r="F53">
-        <v>5</v>
-      </c>
-      <c r="G53" t="s">
-        <v>31</v>
-      </c>
-      <c r="H53">
-        <v>600</v>
-      </c>
-      <c r="I53" t="s">
-        <v>31</v>
-      </c>
-      <c r="J53" t="s">
-        <v>31</v>
-      </c>
-      <c r="K53">
-        <v>90</v>
-      </c>
-      <c r="L53" t="s">
-        <v>31</v>
-      </c>
-      <c r="M53">
-        <v>30</v>
-      </c>
-      <c r="N53" t="s">
-        <v>31</v>
-      </c>
-      <c r="O53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>355</v>
-      </c>
-      <c r="B54" t="s">
-        <v>356</v>
-      </c>
-      <c r="C54" t="s">
-        <v>357</v>
-      </c>
-      <c r="D54" t="s">
-        <v>349</v>
-      </c>
-      <c r="E54" t="s">
-        <v>31</v>
-      </c>
-      <c r="F54">
-        <v>3</v>
-      </c>
-      <c r="G54" t="s">
-        <v>31</v>
-      </c>
-      <c r="H54">
-        <v>900</v>
-      </c>
-      <c r="I54" t="s">
-        <v>31</v>
-      </c>
-      <c r="J54" t="s">
-        <v>31</v>
-      </c>
-      <c r="K54" t="s">
-        <v>31</v>
-      </c>
       <c r="L54">
-        <v>200</v>
-      </c>
-      <c r="M54">
         <v>45</v>
       </c>
+      <c r="M54" t="s">
+        <v>31</v>
+      </c>
       <c r="N54" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7376,57 +7051,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>361</v>
+        <v>307</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>365</v>
+        <v>311</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>367</v>
+        <v>313</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>368</v>
+        <v>314</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>370</v>
+        <v>316</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>371</v>
+        <v>317</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>373</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -7479,7 +7154,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -7532,7 +7207,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7585,7 +7260,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>323</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -7638,7 +7313,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -7691,7 +7366,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>379</v>
+        <v>325</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -7744,7 +7419,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>326</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -7797,7 +7472,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="B9">
         <v>9</v>
@@ -7850,7 +7525,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -7932,45 +7607,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>331</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>386</v>
+        <v>332</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>387</v>
+        <v>333</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>388</v>
+        <v>334</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>394</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -8011,7 +7686,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -8052,7 +7727,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="B4">
         <v>1.1</v>
@@ -8093,7 +7768,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="B5">
         <v>1.1</v>
@@ -8134,7 +7809,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="B6">
         <v>1.25</v>
@@ -8175,7 +7850,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>400</v>
+        <v>346</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -8216,7 +7891,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>401</v>
+        <v>347</v>
       </c>
       <c r="B8">
         <v>1.1</v>
@@ -8257,7 +7932,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>402</v>
+        <v>348</v>
       </c>
       <c r="B9">
         <v>1.15</v>
@@ -8326,16 +8001,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>404</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>405</v>
+        <v>351</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>406</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -8350,42 +8025,42 @@
         <v>107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>407</v>
+        <v>353</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>409</v>
+        <v>355</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>410</v>
+        <v>356</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>414</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>361</v>
       </c>
       <c r="B2" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -8429,16 +8104,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>418</v>
+        <v>364</v>
       </c>
       <c r="B3" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C3" t="s">
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E3">
         <v>0.25</v>
@@ -8482,16 +8157,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>420</v>
+        <v>366</v>
       </c>
       <c r="B4" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -8535,16 +8210,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>423</v>
+        <v>369</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C5" t="s">
         <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -8588,16 +8263,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>371</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E6">
         <v>0.4</v>
@@ -8633,7 +8308,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>427</v>
+        <v>373</v>
       </c>
       <c r="Q6">
         <v>1.25</v>
@@ -8641,16 +8316,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="B7" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E7">
         <v>0.25</v>
@@ -8694,16 +8369,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E8">
         <v>0.25</v>
@@ -8747,16 +8422,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>430</v>
+        <v>376</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E9">
         <v>0.15</v>
@@ -8800,16 +8475,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>431</v>
+        <v>377</v>
       </c>
       <c r="B10" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C10" t="s">
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="E10">
         <v>0.15</v>
@@ -8853,16 +8528,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>433</v>
+        <v>379</v>
       </c>
       <c r="B11" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C11" t="s">
         <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E11">
         <v>0.15</v>
@@ -8906,16 +8581,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>434</v>
+        <v>380</v>
       </c>
       <c r="B12" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C12" t="s">
         <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -8959,16 +8634,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E13">
         <v>0.25</v>
@@ -9012,16 +8687,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="B14" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C14" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E14">
         <v>0.15</v>
@@ -9065,16 +8740,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>383</v>
       </c>
       <c r="B15" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C15" t="s">
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="E15">
         <v>0.15</v>
@@ -9118,16 +8793,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C16" t="s">
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E16">
         <v>0.25</v>
@@ -9171,16 +8846,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E17">
         <v>0.25</v>
@@ -9224,16 +8899,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="B18" t="s">
-        <v>416</v>
+        <v>362</v>
       </c>
       <c r="C18" t="s">
         <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E18">
         <v>0.2</v>
@@ -9277,16 +8952,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="B19" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E19">
         <v>0.3</v>
@@ -9330,16 +9005,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="B20" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C20" t="s">
         <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -9383,16 +9058,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>443</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -9436,16 +9111,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>444</v>
+        <v>390</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -9489,16 +9164,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="B23" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C23" t="s">
         <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="E23">
         <v>0.25</v>
@@ -9542,16 +9217,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="B24" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C24" t="s">
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E24">
         <v>0.3</v>
@@ -9595,16 +9270,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>393</v>
       </c>
       <c r="B25" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -9648,16 +9323,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="B26" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -9701,16 +9376,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>395</v>
       </c>
       <c r="B27" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E27">
         <v>0.25</v>
@@ -9754,16 +9429,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>396</v>
       </c>
       <c r="B28" t="s">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -9807,16 +9482,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>451</v>
+        <v>397</v>
       </c>
       <c r="B29" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C29" t="s">
         <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E29">
         <v>0.45</v>
@@ -9852,7 +9527,7 @@
         <v>2</v>
       </c>
       <c r="P29" t="s">
-        <v>452</v>
+        <v>398</v>
       </c>
       <c r="Q29">
         <v>1.1</v>
@@ -9860,16 +9535,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>453</v>
+        <v>399</v>
       </c>
       <c r="B30" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C30" t="s">
         <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>424</v>
+        <v>370</v>
       </c>
       <c r="E30">
         <v>0.85</v>
@@ -9905,7 +9580,7 @@
         <v>2</v>
       </c>
       <c r="P30" t="s">
-        <v>454</v>
+        <v>400</v>
       </c>
       <c r="Q30">
         <v>1.25</v>
@@ -9913,16 +9588,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>455</v>
+        <v>401</v>
       </c>
       <c r="B31" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>422</v>
+        <v>368</v>
       </c>
       <c r="E31">
         <v>0.85</v>
@@ -9958,7 +9633,7 @@
         <v>2</v>
       </c>
       <c r="P31" t="s">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="Q31">
         <v>1.25</v>
@@ -9966,16 +9641,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>457</v>
+        <v>403</v>
       </c>
       <c r="B32" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="E32">
         <v>0.4</v>
@@ -10011,7 +9686,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="s">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="Q32">
         <v>1.2</v>
@@ -10019,16 +9694,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="B33" t="s">
-        <v>426</v>
+        <v>372</v>
       </c>
       <c r="C33" t="s">
         <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="E33">
         <v>0.4</v>
@@ -10064,7 +9739,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="s">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="Q33">
         <v>1.25</v>
@@ -10097,13 +9772,13 @@
         <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>461</v>
+        <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>462</v>
+        <v>408</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>404</v>
+        <v>350</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>102</v>
@@ -10121,27 +9796,27 @@
         <v>101</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>410</v>
+        <v>356</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>412</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="B2" t="s">
-        <v>464</v>
+        <v>410</v>
       </c>
       <c r="C2" t="s">
-        <v>465</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
-        <v>466</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -10173,16 +9848,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="B3" t="s">
-        <v>468</v>
+        <v>414</v>
       </c>
       <c r="C3" t="s">
-        <v>469</v>
+        <v>415</v>
       </c>
       <c r="D3" t="s">
-        <v>470</v>
+        <v>416</v>
       </c>
       <c r="E3" t="s">
         <v>115</v>
@@ -10214,16 +9889,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="B4" t="s">
-        <v>472</v>
+        <v>418</v>
       </c>
       <c r="C4" t="s">
-        <v>473</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
         <v>114</v>
@@ -10255,16 +9930,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="B5" t="s">
-        <v>476</v>
+        <v>422</v>
       </c>
       <c r="C5" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
       <c r="D5" t="s">
-        <v>478</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
         <v>116</v>
@@ -10296,16 +9971,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="B6" t="s">
-        <v>480</v>
+        <v>426</v>
       </c>
       <c r="C6" t="s">
-        <v>481</v>
+        <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>482</v>
+        <v>428</v>
       </c>
       <c r="E6" t="s">
         <v>115</v>
@@ -10366,51 +10041,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>486</v>
+        <v>432</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>487</v>
+        <v>433</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>488</v>
+        <v>434</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>489</v>
+        <v>435</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>490</v>
+        <v>436</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>491</v>
+        <v>437</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>494</v>
+        <v>440</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>495</v>
+        <v>441</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="B2" t="s">
         <v>161</v>
@@ -10457,7 +10132,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="B3" t="s">
         <v>162</v>
@@ -10525,27 +10200,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>499</v>
+        <v>445</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>501</v>
+        <v>447</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="B2">
         <v>0.99</v>
@@ -10568,7 +10243,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>506</v>
+        <v>452</v>
       </c>
       <c r="B3">
         <v>4.99</v>
@@ -10591,7 +10266,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>453</v>
       </c>
       <c r="B4">
         <v>9.99</v>
@@ -10614,7 +10289,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="B5">
         <v>19.99</v>
@@ -10637,7 +10312,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>455</v>
       </c>
       <c r="B6">
         <v>49.99</v>
@@ -10660,7 +10335,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>510</v>
+        <v>456</v>
       </c>
       <c r="B7">
         <v>99.99</v>
@@ -10683,7 +10358,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="B8">
         <v>9.99</v>
@@ -10706,7 +10381,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="B9">
         <v>4.99</v>
@@ -10729,7 +10404,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>513</v>
+        <v>459</v>
       </c>
       <c r="B10">
         <v>4.99</v>
@@ -10741,7 +10416,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -10752,7 +10427,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>514</v>
+        <v>460</v>
       </c>
       <c r="B11">
         <v>9.99</v>
@@ -10764,7 +10439,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -10775,7 +10450,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c r="B12">
         <v>19.99</v>
@@ -10787,7 +10462,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -10819,48 +10494,48 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>516</v>
+        <v>462</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>519</v>
+        <v>465</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>520</v>
+        <v>466</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>521</v>
+        <v>467</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>522</v>
+        <v>468</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>523</v>
+        <v>469</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>524</v>
+        <v>470</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>525</v>
+        <v>471</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>526</v>
+        <v>472</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>527</v>
+        <v>473</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>528</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -10881,10 +10556,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="I2" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="J2">
         <v>25</v>
@@ -10901,7 +10576,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10922,10 +10597,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="I3" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="J3">
         <v>40</v>
@@ -10942,7 +10617,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -10963,10 +10638,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="I4" t="s">
-        <v>463</v>
+        <v>409</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -10983,7 +10658,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -11004,10 +10679,10 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="I5" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="J5">
         <v>75</v>
@@ -11024,7 +10699,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -11045,10 +10720,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="I6" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="J6">
         <v>110</v>
@@ -11065,7 +10740,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -11086,10 +10761,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="I7" t="s">
-        <v>467</v>
+        <v>413</v>
       </c>
       <c r="J7">
         <v>150</v>
@@ -11106,7 +10781,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>531</v>
+        <v>477</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -11127,10 +10802,10 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="I8" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="J8">
         <v>200</v>
@@ -11147,7 +10822,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>477</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -11168,10 +10843,10 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="I9" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="J9">
         <v>280</v>
@@ -11188,7 +10863,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>531</v>
+        <v>477</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -11209,10 +10884,10 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="I10" t="s">
-        <v>471</v>
+        <v>417</v>
       </c>
       <c r="J10">
         <v>380</v>
@@ -11229,7 +10904,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>532</v>
+        <v>478</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -11250,10 +10925,10 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="I11" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="J11">
         <v>450</v>
@@ -11270,7 +10945,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>532</v>
+        <v>478</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11291,10 +10966,10 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="I12" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="J12">
         <v>600</v>
@@ -11311,7 +10986,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>532</v>
+        <v>478</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11332,10 +11007,10 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="I13" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="J13">
         <v>800</v>
@@ -11352,7 +11027,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>533</v>
+        <v>479</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -11373,10 +11048,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="I14" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -11393,7 +11068,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>533</v>
+        <v>479</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -11414,10 +11089,10 @@
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="I15" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="J15">
         <v>1300</v>
@@ -11434,7 +11109,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>533</v>
+        <v>479</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -11455,10 +11130,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="I16" t="s">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="J16">
         <v>1700</v>
@@ -11495,19 +11170,19 @@
         <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>534</v>
+        <v>480</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>525</v>
+        <v>471</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>526</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>527</v>
+        <v>473</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>528</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11626,15 +11301,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>429</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>535</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>536</v>
+        <v>482</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11642,7 +11317,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>537</v>
+        <v>483</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -11650,7 +11325,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>538</v>
+        <v>484</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -11658,7 +11333,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>539</v>
+        <v>485</v>
       </c>
       <c r="B5">
         <v>30</v>
@@ -11666,15 +11341,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>540</v>
+        <v>486</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>541</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>542</v>
+        <v>488</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -11682,7 +11357,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>543</v>
+        <v>489</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -11690,7 +11365,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>544</v>
+        <v>490</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -11698,7 +11373,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>545</v>
+        <v>491</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -11706,7 +11381,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>546</v>
+        <v>492</v>
       </c>
       <c r="B11">
         <v>300</v>
@@ -11714,15 +11389,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>547</v>
+        <v>493</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>548</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>549</v>
+        <v>495</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -11730,7 +11405,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>550</v>
+        <v>496</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -11738,7 +11413,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>551</v>
+        <v>497</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -11746,7 +11421,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>552</v>
+        <v>498</v>
       </c>
       <c r="B16">
         <v>1.25</v>
@@ -11754,7 +11429,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>553</v>
+        <v>499</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -11762,15 +11437,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>554</v>
+        <v>500</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>555</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>556</v>
+        <v>502</v>
       </c>
       <c r="B19">
         <v>10</v>
@@ -11778,7 +11453,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>557</v>
+        <v>503</v>
       </c>
       <c r="B20">
         <v>1.05</v>
@@ -11786,7 +11461,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>558</v>
+        <v>504</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -11794,7 +11469,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>559</v>
+        <v>505</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -11802,7 +11477,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>560</v>
+        <v>506</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -11810,15 +11485,15 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>561</v>
+        <v>507</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>562</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>563</v>
+        <v>509</v>
       </c>
       <c r="B25">
         <v>1.05</v>
@@ -11826,7 +11501,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>564</v>
+        <v>510</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -11834,7 +11509,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>565</v>
+        <v>511</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -11842,7 +11517,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>566</v>
+        <v>512</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -11850,7 +11525,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="B29">
         <v>2500</v>
@@ -11858,7 +11533,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -11866,7 +11541,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="B31">
         <v>0.1</v>
@@ -11874,7 +11549,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -11882,7 +11557,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -11890,7 +11565,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>572</v>
+        <v>518</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -11898,7 +11573,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>573</v>
+        <v>519</v>
       </c>
       <c r="B35">
         <v>50</v>
@@ -11906,7 +11581,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>574</v>
+        <v>520</v>
       </c>
       <c r="B36">
         <v>250</v>
@@ -11914,7 +11589,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>575</v>
+        <v>521</v>
       </c>
       <c r="B37">
         <v>2000</v>
@@ -11922,7 +11597,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>576</v>
+        <v>522</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -11930,47 +11605,47 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>577</v>
+        <v>523</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>578</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>579</v>
+        <v>525</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>580</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>581</v>
+        <v>527</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>582</v>
+        <v>528</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>583</v>
+        <v>529</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>584</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>585</v>
+        <v>531</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>586</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>587</v>
+        <v>533</v>
       </c>
       <c r="B44">
         <v>20000</v>
@@ -11978,7 +11653,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>588</v>
+        <v>534</v>
       </c>
       <c r="B45">
         <v>100</v>
@@ -11986,7 +11661,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>589</v>
+        <v>535</v>
       </c>
       <c r="B46">
         <v>150</v>
@@ -11994,7 +11669,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>590</v>
+        <v>536</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -12002,71 +11677,71 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>591</v>
+        <v>537</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>592</v>
+        <v>538</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>593</v>
+        <v>539</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>594</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>595</v>
+        <v>541</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>596</v>
+        <v>542</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>597</v>
+        <v>543</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>598</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>599</v>
+        <v>545</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>600</v>
+        <v>546</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>601</v>
+        <v>547</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>602</v>
+        <v>548</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>603</v>
+        <v>549</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>605</v>
+        <v>551</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>606</v>
+        <v>552</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>607</v>
+        <v>553</v>
       </c>
       <c r="B56">
         <v>8</v>
@@ -12074,7 +11749,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>608</v>
+        <v>554</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -12082,7 +11757,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>609</v>
+        <v>555</v>
       </c>
       <c r="B58">
         <v>8</v>
@@ -12090,7 +11765,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>610</v>
+        <v>556</v>
       </c>
       <c r="B59">
         <v>4</v>
@@ -12098,7 +11773,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="B60">
         <v>12</v>
@@ -12106,7 +11781,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>612</v>
+        <v>558</v>
       </c>
       <c r="B61">
         <v>40</v>
@@ -12114,7 +11789,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>613</v>
+        <v>559</v>
       </c>
       <c r="B62">
         <v>60</v>
@@ -12122,103 +11797,103 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>614</v>
+        <v>560</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>615</v>
+        <v>561</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>616</v>
+        <v>562</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>617</v>
+        <v>563</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>618</v>
+        <v>564</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>619</v>
+        <v>565</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>620</v>
+        <v>566</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>621</v>
+        <v>567</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>622</v>
+        <v>568</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>623</v>
+        <v>569</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>624</v>
+        <v>570</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>615</v>
+        <v>561</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>625</v>
+        <v>571</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>615</v>
+        <v>561</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>626</v>
+        <v>572</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>627</v>
+        <v>573</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>628</v>
+        <v>574</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>617</v>
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>629</v>
+        <v>575</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>630</v>
+        <v>576</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>631</v>
+        <v>577</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>375</v>
+        <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>632</v>
+        <v>578</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>374</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>633</v>
+        <v>579</v>
       </c>
       <c r="B75">
         <v>15</v>
@@ -12226,7 +11901,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>634</v>
+        <v>580</v>
       </c>
       <c r="B76">
         <v>0.5</v>
@@ -12234,7 +11909,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>635</v>
+        <v>581</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -12242,7 +11917,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -12250,7 +11925,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>637</v>
+        <v>583</v>
       </c>
       <c r="B79">
         <v>2500</v>
@@ -12258,7 +11933,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>638</v>
+        <v>584</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -12266,7 +11941,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>639</v>
+        <v>585</v>
       </c>
       <c r="B81">
         <v>100</v>
@@ -12274,7 +11949,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>640</v>
+        <v>586</v>
       </c>
       <c r="B82">
         <v>12</v>
@@ -12282,23 +11957,23 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>641</v>
+        <v>587</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>642</v>
+        <v>588</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>643</v>
+        <v>589</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>644</v>
+        <v>590</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>645</v>
+        <v>591</v>
       </c>
       <c r="B85">
         <v>10</v>
@@ -12306,7 +11981,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>646</v>
+        <v>592</v>
       </c>
       <c r="B86">
         <v>30</v>
@@ -12314,15 +11989,15 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>647</v>
+        <v>593</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>648</v>
+        <v>594</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>649</v>
+        <v>595</v>
       </c>
       <c r="B88">
         <v>28</v>
@@ -12330,7 +12005,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>650</v>
+        <v>596</v>
       </c>
       <c r="B89">
         <v>2000</v>
@@ -12338,7 +12013,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>651</v>
+        <v>597</v>
       </c>
       <c r="B90">
         <v>25000</v>
@@ -12346,31 +12021,31 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>652</v>
+        <v>598</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>653</v>
+        <v>599</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>654</v>
+        <v>600</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>655</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>656</v>
+        <v>602</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>657</v>
+        <v>603</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>658</v>
+        <v>604</v>
       </c>
       <c r="B94">
         <v>60</v>
@@ -12378,15 +12053,15 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>659</v>
+        <v>605</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>660</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>661</v>
+        <v>607</v>
       </c>
       <c r="B96">
         <v>30</v>
@@ -12394,23 +12069,23 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>662</v>
+        <v>608</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>663</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>664</v>
+        <v>610</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>665</v>
+        <v>611</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>666</v>
+        <v>612</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -12418,7 +12093,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>667</v>
+        <v>613</v>
       </c>
       <c r="B100">
         <v>24</v>
@@ -12426,7 +12101,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>668</v>
+        <v>614</v>
       </c>
       <c r="B101">
         <v>10</v>
@@ -12434,7 +12109,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>669</v>
+        <v>615</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -12442,7 +12117,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>670</v>
+        <v>616</v>
       </c>
       <c r="B103">
         <v>10</v>
@@ -12450,7 +12125,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>671</v>
+        <v>617</v>
       </c>
       <c r="B104">
         <v>2</v>
@@ -12458,7 +12133,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>672</v>
+        <v>618</v>
       </c>
       <c r="B105">
         <v>50</v>
@@ -12466,7 +12141,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>673</v>
+        <v>619</v>
       </c>
       <c r="B106">
         <v>2</v>
@@ -12474,7 +12149,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>674</v>
+        <v>620</v>
       </c>
       <c r="B107">
         <v>100</v>
@@ -12482,7 +12157,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>675</v>
+        <v>621</v>
       </c>
       <c r="B108">
         <v>1.09</v>
@@ -12490,7 +12165,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>676</v>
+        <v>622</v>
       </c>
       <c r="B109">
         <v>10</v>
@@ -12498,7 +12173,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>677</v>
+        <v>623</v>
       </c>
       <c r="B110">
         <v>50</v>
@@ -12506,7 +12181,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>678</v>
+        <v>624</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -12514,7 +12189,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>679</v>
+        <v>625</v>
       </c>
       <c r="B112">
         <v>0.2</v>
@@ -12522,7 +12197,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>680</v>
+        <v>626</v>
       </c>
       <c r="B113">
         <v>0.2</v>
@@ -12530,7 +12205,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>681</v>
+        <v>627</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -12538,7 +12213,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>682</v>
+        <v>628</v>
       </c>
       <c r="B115">
         <v>0.3</v>
@@ -12546,7 +12221,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>683</v>
+        <v>629</v>
       </c>
       <c r="B116">
         <v>1.5</v>
@@ -12554,7 +12229,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>684</v>
+        <v>630</v>
       </c>
       <c r="B117">
         <v>0.75</v>
@@ -12562,7 +12237,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>685</v>
+        <v>631</v>
       </c>
       <c r="B118">
         <v>0.4</v>
@@ -12570,7 +12245,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>686</v>
+        <v>632</v>
       </c>
       <c r="B119">
         <v>100</v>
@@ -12578,7 +12253,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>687</v>
+        <v>633</v>
       </c>
       <c r="B120">
         <v>600</v>
@@ -12586,7 +12261,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>688</v>
+        <v>634</v>
       </c>
       <c r="B121">
         <v>3</v>
@@ -12594,7 +12269,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>689</v>
+        <v>635</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -12602,7 +12277,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>690</v>
+        <v>636</v>
       </c>
       <c r="B123">
         <v>3</v>
@@ -12610,7 +12285,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>691</v>
+        <v>637</v>
       </c>
       <c r="B124">
         <v>4</v>
@@ -12618,7 +12293,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>692</v>
+        <v>638</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -12626,7 +12301,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>693</v>
+        <v>639</v>
       </c>
       <c r="B126">
         <v>6</v>
@@ -12634,7 +12309,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>694</v>
+        <v>640</v>
       </c>
       <c r="B127">
         <v>400</v>
@@ -12642,7 +12317,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>695</v>
+        <v>641</v>
       </c>
       <c r="B128">
         <v>0.3</v>
@@ -12650,7 +12325,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>696</v>
+        <v>642</v>
       </c>
       <c r="B129">
         <v>3</v>
@@ -12658,7 +12333,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>697</v>
+        <v>643</v>
       </c>
       <c r="B130">
         <v>0.5</v>
@@ -12666,7 +12341,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>698</v>
+        <v>644</v>
       </c>
       <c r="B131">
         <v>0.1</v>
@@ -12674,7 +12349,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>699</v>
+        <v>645</v>
       </c>
       <c r="B132">
         <v>0.3</v>
@@ -12682,7 +12357,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>700</v>
+        <v>646</v>
       </c>
       <c r="B133">
         <v>0.25</v>
@@ -12690,7 +12365,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>701</v>
+        <v>647</v>
       </c>
       <c r="B134">
         <v>500</v>
@@ -12698,7 +12373,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>702</v>
+        <v>648</v>
       </c>
       <c r="B135">
         <v>15</v>
@@ -12706,7 +12381,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="B136">
         <v>150</v>
@@ -12714,7 +12389,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>704</v>
+        <v>650</v>
       </c>
       <c r="B137">
         <v>6</v>
@@ -12722,7 +12397,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>705</v>
+        <v>651</v>
       </c>
       <c r="B138">
         <v>3</v>
@@ -12730,7 +12405,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>706</v>
+        <v>652</v>
       </c>
       <c r="B139">
         <v>2500</v>
@@ -12738,7 +12413,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>707</v>
+        <v>653</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -12746,7 +12421,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>708</v>
+        <v>654</v>
       </c>
       <c r="B141">
         <v>30</v>
@@ -12754,7 +12429,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>709</v>
+        <v>655</v>
       </c>
       <c r="B142">
         <v>90</v>
@@ -12762,7 +12437,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>710</v>
+        <v>656</v>
       </c>
       <c r="B143">
         <v>0.5</v>
@@ -12770,7 +12445,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>711</v>
+        <v>657</v>
       </c>
       <c r="B144">
         <v>5</v>
@@ -12778,7 +12453,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>712</v>
+        <v>658</v>
       </c>
       <c r="B145">
         <v>5</v>
@@ -12786,10 +12461,10 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>713</v>
+        <v>659</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>714</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
